--- a/research/traditional_assets/database/data/jamaica/jamaica_trucking.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_trucking.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="jmse_kex" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.038</v>
+        <v>0.0969</v>
+      </c>
+      <c r="E2">
+        <v>-0.0435</v>
       </c>
       <c r="G2">
-        <v>0.05824847250509164</v>
+        <v>0.2165898617511521</v>
       </c>
       <c r="H2">
-        <v>0.05824847250509164</v>
+        <v>0.2165898617511521</v>
       </c>
       <c r="I2">
-        <v>-0.05865580448065173</v>
+        <v>0.1993087557603687</v>
       </c>
       <c r="J2">
-        <v>-0.05865580448065173</v>
+        <v>0.171572782056653</v>
       </c>
       <c r="K2">
-        <v>-0.408</v>
+        <v>1.02</v>
       </c>
       <c r="L2">
-        <v>-0.08309572301425661</v>
+        <v>0.1175115207373272</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.469</v>
+        <v>0.637</v>
       </c>
       <c r="V2">
-        <v>0.01724264705882353</v>
+        <v>0.02219512195121951</v>
       </c>
       <c r="W2">
-        <v>-0.08127490039840637</v>
+        <v>0.2261640798226164</v>
       </c>
       <c r="X2">
-        <v>0.1102821916748895</v>
+        <v>0.1738478088218358</v>
       </c>
       <c r="Y2">
-        <v>-0.1915570920732958</v>
+        <v>0.05231627100078065</v>
       </c>
       <c r="Z2">
-        <v>0.7693513005327484</v>
+        <v>1.171231952503036</v>
       </c>
       <c r="AA2">
-        <v>-0.04512691946098402</v>
+        <v>0.2009515245245916</v>
       </c>
       <c r="AB2">
-        <v>0.1045148720800192</v>
+        <v>0.1655177580542989</v>
       </c>
       <c r="AC2">
-        <v>-0.1496417915410032</v>
+        <v>0.0354337664702927</v>
       </c>
       <c r="AD2">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AG2">
-        <v>2.931</v>
+        <v>2.733</v>
       </c>
       <c r="AH2">
-        <v>0.1111111111111111</v>
+        <v>0.1050826317430621</v>
       </c>
       <c r="AI2">
-        <v>0.4298356510745891</v>
+        <v>0.3756967670011149</v>
       </c>
       <c r="AJ2">
-        <v>0.09727523148916399</v>
+        <v>0.08694683930900646</v>
       </c>
       <c r="AK2">
-        <v>0.3938986695336649</v>
+        <v>0.327973118924757</v>
       </c>
       <c r="AL2">
-        <v>0.052</v>
+        <v>0.169</v>
       </c>
       <c r="AM2">
-        <v>0.051</v>
+        <v>0.158</v>
       </c>
       <c r="AN2">
-        <v>5.84192439862543</v>
+        <v>1.276515151515152</v>
       </c>
       <c r="AO2">
-        <v>-5.538461538461538</v>
+        <v>10.23668639053254</v>
       </c>
       <c r="AP2">
-        <v>5.036082474226805</v>
+        <v>1.035227272727273</v>
       </c>
       <c r="AQ2">
-        <v>-5.647058823529412</v>
+        <v>10.94936708860759</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.038</v>
+        <v>0.0969</v>
+      </c>
+      <c r="E3">
+        <v>-0.0435</v>
       </c>
       <c r="G3">
-        <v>0.05824847250509164</v>
+        <v>0.2165898617511521</v>
       </c>
       <c r="H3">
-        <v>0.05824847250509164</v>
+        <v>0.2165898617511521</v>
       </c>
       <c r="I3">
-        <v>-0.05865580448065173</v>
+        <v>0.1993087557603687</v>
       </c>
       <c r="J3">
-        <v>-0.05865580448065173</v>
+        <v>0.171572782056653</v>
       </c>
       <c r="K3">
-        <v>-0.408</v>
+        <v>1.02</v>
       </c>
       <c r="L3">
-        <v>-0.08309572301425661</v>
+        <v>0.1175115207373272</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.469</v>
+        <v>0.637</v>
       </c>
       <c r="V3">
-        <v>0.01724264705882353</v>
+        <v>0.02219512195121951</v>
       </c>
       <c r="W3">
-        <v>-0.08127490039840637</v>
+        <v>0.2261640798226164</v>
       </c>
       <c r="X3">
-        <v>0.1102821916748895</v>
+        <v>0.1738478088218358</v>
       </c>
       <c r="Y3">
-        <v>-0.1915570920732958</v>
+        <v>0.05231627100078065</v>
       </c>
       <c r="Z3">
-        <v>0.7693513005327484</v>
+        <v>1.171231952503036</v>
       </c>
       <c r="AA3">
-        <v>-0.04512691946098402</v>
+        <v>0.2009515245245916</v>
       </c>
       <c r="AB3">
-        <v>0.1045148720800192</v>
+        <v>0.1655177580542989</v>
       </c>
       <c r="AC3">
-        <v>-0.1496417915410032</v>
+        <v>0.0354337664702927</v>
       </c>
       <c r="AD3">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="AG3">
-        <v>2.931</v>
+        <v>2.733</v>
       </c>
       <c r="AH3">
+        <v>0.1050826317430621</v>
+      </c>
+      <c r="AI3">
+        <v>0.3756967670011149</v>
+      </c>
+      <c r="AJ3">
+        <v>0.08694683930900646</v>
+      </c>
+      <c r="AK3">
+        <v>0.327973118924757</v>
+      </c>
+      <c r="AL3">
+        <v>0.169</v>
+      </c>
+      <c r="AM3">
+        <v>0.158</v>
+      </c>
+      <c r="AN3">
+        <v>1.276515151515152</v>
+      </c>
+      <c r="AO3">
+        <v>10.23668639053254</v>
+      </c>
+      <c r="AP3">
+        <v>1.035227272727273</v>
+      </c>
+      <c r="AQ3">
+        <v>10.94936708860759</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Knutsford Express Services Limited (JMSE:KEX)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>JMSE:KEX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Trucking</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.105082631743062</v>
+      </c>
+      <c r="F2">
+        <v>0.21</v>
+      </c>
+      <c r="G2">
+        <v>28.7</v>
+      </c>
+      <c r="H2">
+        <v>27.624507513827</v>
+      </c>
+      <c r="I2">
+        <v>31.433</v>
+      </c>
+      <c r="J2">
+        <v>33.722207513827</v>
+      </c>
+      <c r="K2">
+        <v>3.37</v>
+      </c>
+      <c r="L2">
+        <v>6.7347</v>
+      </c>
+      <c r="M2">
+        <v>0.165517758054299</v>
+      </c>
+      <c r="N2">
+        <v>0.156915615274818</v>
+      </c>
+      <c r="O2">
+        <v>0.094576376146789</v>
+      </c>
+      <c r="P2">
+        <v>0.04125</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.173847808821836</v>
+      </c>
+      <c r="T2">
+        <v>0.187662171233947</v>
+      </c>
+      <c r="U2">
+        <v>0.876478356777955</v>
+      </c>
+      <c r="V2">
+        <v>0.966135418025622</v>
+      </c>
+      <c r="W2">
+        <v>4.640822227351694</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>28.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.1540800269367614</v>
+      </c>
+      <c r="AC2">
+        <v>0.1261018348623854</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>2.64</v>
+      </c>
+      <c r="AH2">
+        <v>0.921</v>
+      </c>
+      <c r="AI2">
+        <v>1.12</v>
+      </c>
+      <c r="AJ2">
+        <v>3.37</v>
+      </c>
+      <c r="AK2">
+        <v>3.37</v>
+      </c>
+      <c r="AL2">
+        <v>0.169</v>
+      </c>
+      <c r="AM2">
+        <v>3.37</v>
+      </c>
+      <c r="AN2">
+        <v>0.637</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1629172720578556</v>
+      </c>
+      <c r="C2">
+        <v>32.72857938199044</v>
+      </c>
+      <c r="D2">
+        <v>32.09157938199044</v>
+      </c>
+      <c r="E2">
+        <v>-3.37</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.637</v>
+      </c>
+      <c r="H2">
+        <v>28.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.64</v>
+      </c>
+      <c r="K2">
+        <v>0.921</v>
+      </c>
+      <c r="L2">
+        <v>1.719</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.719</v>
+      </c>
+      <c r="O2">
+        <v>0.42975</v>
+      </c>
+      <c r="P2">
+        <v>1.28925</v>
+      </c>
+      <c r="Q2">
+        <v>2.21025</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1629172720578556</v>
+      </c>
+      <c r="T2">
+        <v>0.8055377100160859</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.162561728877711</v>
+      </c>
+      <c r="C3">
+        <v>32.50007219711029</v>
+      </c>
+      <c r="D3">
+        <v>32.18377219711029</v>
+      </c>
+      <c r="E3">
+        <v>-3.0493</v>
+      </c>
+      <c r="F3">
+        <v>0.3207</v>
+      </c>
+      <c r="G3">
+        <v>0.637</v>
+      </c>
+      <c r="H3">
+        <v>28.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.64</v>
+      </c>
+      <c r="K3">
+        <v>0.921</v>
+      </c>
+      <c r="L3">
+        <v>1.719</v>
+      </c>
+      <c r="M3">
+        <v>0.01465599</v>
+      </c>
+      <c r="N3">
+        <v>1.70434401</v>
+      </c>
+      <c r="O3">
+        <v>0.4260860025</v>
+      </c>
+      <c r="P3">
+        <v>1.2782580075</v>
+      </c>
+      <c r="Q3">
+        <v>2.1992580075</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1638575544219303</v>
+      </c>
+      <c r="T3">
+        <v>0.8116402684252987</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>117.2899271901796</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1622061856975663</v>
+      </c>
+      <c r="C4">
+        <v>32.2720962421112</v>
+      </c>
+      <c r="D4">
+        <v>32.2764962421112</v>
+      </c>
+      <c r="E4">
+        <v>-2.7286</v>
+      </c>
+      <c r="F4">
+        <v>0.6414</v>
+      </c>
+      <c r="G4">
+        <v>0.637</v>
+      </c>
+      <c r="H4">
+        <v>28.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.64</v>
+      </c>
+      <c r="K4">
+        <v>0.921</v>
+      </c>
+      <c r="L4">
+        <v>1.719</v>
+      </c>
+      <c r="M4">
+        <v>0.02931198</v>
+      </c>
+      <c r="N4">
+        <v>1.68968802</v>
+      </c>
+      <c r="O4">
+        <v>0.422422005</v>
+      </c>
+      <c r="P4">
+        <v>1.267266015</v>
+      </c>
+      <c r="Q4">
+        <v>2.188266015</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1648170262220065</v>
+      </c>
+      <c r="T4">
+        <v>0.8178673688428627</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>58.64496359508979</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1618506425174217</v>
+      </c>
+      <c r="C5">
+        <v>32.04465612180847</v>
+      </c>
+      <c r="D5">
+        <v>32.36975612180847</v>
+      </c>
+      <c r="E5">
+        <v>-2.4079</v>
+      </c>
+      <c r="F5">
+        <v>0.9621</v>
+      </c>
+      <c r="G5">
+        <v>0.637</v>
+      </c>
+      <c r="H5">
+        <v>28.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.64</v>
+      </c>
+      <c r="K5">
+        <v>0.921</v>
+      </c>
+      <c r="L5">
+        <v>1.719</v>
+      </c>
+      <c r="M5">
+        <v>0.04396797</v>
+      </c>
+      <c r="N5">
+        <v>1.67503203</v>
+      </c>
+      <c r="O5">
+        <v>0.4187580075</v>
+      </c>
+      <c r="P5">
+        <v>1.2562740225</v>
+      </c>
+      <c r="Q5">
+        <v>2.1772740225</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1657962809457956</v>
+      </c>
+      <c r="T5">
+        <v>0.8242228630834693</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.034275</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>39.09664239672653</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1614950993372771</v>
+      </c>
+      <c r="C6">
+        <v>31.81775649439236</v>
+      </c>
+      <c r="D6">
+        <v>32.46355649439236</v>
+      </c>
+      <c r="E6">
+        <v>-2.0872</v>
+      </c>
+      <c r="F6">
+        <v>1.2828</v>
+      </c>
+      <c r="G6">
+        <v>0.637</v>
+      </c>
+      <c r="H6">
+        <v>28.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.64</v>
+      </c>
+      <c r="K6">
+        <v>0.921</v>
+      </c>
+      <c r="L6">
+        <v>1.719</v>
+      </c>
+      <c r="M6">
+        <v>0.05862396</v>
+      </c>
+      <c r="N6">
+        <v>1.66037604</v>
+      </c>
+      <c r="O6">
+        <v>0.41509401</v>
+      </c>
+      <c r="P6">
+        <v>1.24528203</v>
+      </c>
+      <c r="Q6">
+        <v>2.16628203</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1667959368096636</v>
+      </c>
+      <c r="T6">
+        <v>0.8307107634540886</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.034275</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>29.3224817975449</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1611395561571324</v>
+      </c>
+      <c r="C7">
+        <v>31.59140207220367</v>
+      </c>
+      <c r="D7">
+        <v>32.55790207220367</v>
+      </c>
+      <c r="E7">
+        <v>-1.7665</v>
+      </c>
+      <c r="F7">
+        <v>1.6035</v>
+      </c>
+      <c r="G7">
+        <v>0.637</v>
+      </c>
+      <c r="H7">
+        <v>28.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.64</v>
+      </c>
+      <c r="K7">
+        <v>0.921</v>
+      </c>
+      <c r="L7">
+        <v>1.719</v>
+      </c>
+      <c r="M7">
+        <v>0.07327995000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.64572005</v>
+      </c>
+      <c r="O7">
+        <v>0.4114300125</v>
+      </c>
+      <c r="P7">
+        <v>1.2342900375</v>
+      </c>
+      <c r="Q7">
+        <v>2.1552900375</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1678166380601394</v>
+      </c>
+      <c r="T7">
+        <v>0.8373352512009313</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.034275</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>23.45798543803591</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1607840129769878</v>
+      </c>
+      <c r="C8">
+        <v>31.36559762252281</v>
+      </c>
+      <c r="D8">
+        <v>32.6527976225228</v>
+      </c>
+      <c r="E8">
+        <v>-1.4458</v>
+      </c>
+      <c r="F8">
+        <v>1.9242</v>
+      </c>
+      <c r="G8">
+        <v>0.637</v>
+      </c>
+      <c r="H8">
+        <v>28.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.64</v>
+      </c>
+      <c r="K8">
+        <v>0.921</v>
+      </c>
+      <c r="L8">
+        <v>1.719</v>
+      </c>
+      <c r="M8">
+        <v>0.08793594</v>
+      </c>
+      <c r="N8">
+        <v>1.63106406</v>
+      </c>
+      <c r="O8">
+        <v>0.407766015</v>
+      </c>
+      <c r="P8">
+        <v>1.223298045</v>
+      </c>
+      <c r="Q8">
+        <v>2.144298045</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1688590563584977</v>
+      </c>
+      <c r="T8">
+        <v>0.8441006854955794</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.034275</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>19.54832119836326</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1604284697968431</v>
+      </c>
+      <c r="C9">
+        <v>31.14034796837293</v>
+      </c>
+      <c r="D9">
+        <v>32.74824796837293</v>
+      </c>
+      <c r="E9">
+        <v>-1.1251</v>
+      </c>
+      <c r="F9">
+        <v>2.2449</v>
+      </c>
+      <c r="G9">
+        <v>0.637</v>
+      </c>
+      <c r="H9">
+        <v>28.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.64</v>
+      </c>
+      <c r="K9">
+        <v>0.921</v>
+      </c>
+      <c r="L9">
+        <v>1.719</v>
+      </c>
+      <c r="M9">
+        <v>0.10259193</v>
+      </c>
+      <c r="N9">
+        <v>1.61640807</v>
+      </c>
+      <c r="O9">
+        <v>0.4041020175</v>
+      </c>
+      <c r="P9">
+        <v>1.2123060525</v>
+      </c>
+      <c r="Q9">
+        <v>2.1333060525</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1699238922546701</v>
+      </c>
+      <c r="T9">
+        <v>0.8510116130008649</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.034275</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>16.75570388431137</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1600729266166985</v>
+      </c>
+      <c r="C10">
+        <v>30.91565798933697</v>
+      </c>
+      <c r="D10">
+        <v>32.84425798933697</v>
+      </c>
+      <c r="E10">
+        <v>-0.8044000000000002</v>
+      </c>
+      <c r="F10">
+        <v>2.5656</v>
+      </c>
+      <c r="G10">
+        <v>0.637</v>
+      </c>
+      <c r="H10">
+        <v>28.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.64</v>
+      </c>
+      <c r="K10">
+        <v>0.921</v>
+      </c>
+      <c r="L10">
+        <v>1.719</v>
+      </c>
+      <c r="M10">
+        <v>0.11724792</v>
+      </c>
+      <c r="N10">
+        <v>1.60175208</v>
+      </c>
+      <c r="O10">
+        <v>0.40043802</v>
+      </c>
+      <c r="P10">
+        <v>1.20131406</v>
+      </c>
+      <c r="Q10">
+        <v>2.12231406</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.171011876757281</v>
+      </c>
+      <c r="T10">
+        <v>0.8580727780606132</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.034275</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>14.66124089877245</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1597173834365539</v>
+      </c>
+      <c r="C11">
+        <v>30.6915326223892</v>
+      </c>
+      <c r="D11">
+        <v>32.94083262238919</v>
+      </c>
+      <c r="E11">
+        <v>-0.4837000000000002</v>
+      </c>
+      <c r="F11">
+        <v>2.8863</v>
+      </c>
+      <c r="G11">
+        <v>0.637</v>
+      </c>
+      <c r="H11">
+        <v>28.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.64</v>
+      </c>
+      <c r="K11">
+        <v>0.921</v>
+      </c>
+      <c r="L11">
+        <v>1.719</v>
+      </c>
+      <c r="M11">
+        <v>0.13190391</v>
+      </c>
+      <c r="N11">
+        <v>1.58709609</v>
+      </c>
+      <c r="O11">
+        <v>0.3967740225</v>
+      </c>
+      <c r="P11">
+        <v>1.1903220675</v>
+      </c>
+      <c r="Q11">
+        <v>2.1113220675</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1721237730072021</v>
+      </c>
+      <c r="T11">
+        <v>0.865289133561235</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.034275</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>13.03221413224218</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1594818402564093</v>
+      </c>
+      <c r="C12">
+        <v>30.43512554712422</v>
+      </c>
+      <c r="D12">
+        <v>33.00512554712422</v>
+      </c>
+      <c r="E12">
+        <v>-0.1629999999999998</v>
+      </c>
+      <c r="F12">
+        <v>3.207</v>
+      </c>
+      <c r="G12">
+        <v>0.637</v>
+      </c>
+      <c r="H12">
+        <v>28.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.64</v>
+      </c>
+      <c r="K12">
+        <v>0.921</v>
+      </c>
+      <c r="L12">
+        <v>1.719</v>
+      </c>
+      <c r="M12">
+        <v>0.1516911</v>
+      </c>
+      <c r="N12">
+        <v>1.5673089</v>
+      </c>
+      <c r="O12">
+        <v>0.391827225</v>
+      </c>
+      <c r="P12">
+        <v>1.175481675</v>
+      </c>
+      <c r="Q12">
+        <v>2.096481675</v>
+      </c>
+      <c r="R12">
         <v>0.1111111111111111</v>
       </c>
-      <c r="AI3">
-        <v>0.4298356510745891</v>
-      </c>
-      <c r="AJ3">
-        <v>0.09727523148916399</v>
-      </c>
-      <c r="AK3">
-        <v>0.3938986695336649</v>
-      </c>
-      <c r="AL3">
-        <v>0.052</v>
-      </c>
-      <c r="AM3">
-        <v>0.051</v>
-      </c>
-      <c r="AN3">
-        <v>5.84192439862543</v>
-      </c>
-      <c r="AO3">
-        <v>-5.538461538461538</v>
-      </c>
-      <c r="AP3">
-        <v>5.036082474226805</v>
-      </c>
-      <c r="AQ3">
-        <v>-5.647058823529412</v>
+      <c r="S12">
+        <v>0.1732603780626769</v>
+      </c>
+      <c r="T12">
+        <v>0.8726658525174263</v>
+      </c>
+      <c r="U12">
+        <v>0.0473</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.035475</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>11.33224032260297</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1591382970762646</v>
+      </c>
+      <c r="C13">
+        <v>30.20864896616052</v>
+      </c>
+      <c r="D13">
+        <v>33.09934896616052</v>
+      </c>
+      <c r="E13">
+        <v>0.1576999999999997</v>
+      </c>
+      <c r="F13">
+        <v>3.5277</v>
+      </c>
+      <c r="G13">
+        <v>0.637</v>
+      </c>
+      <c r="H13">
+        <v>28.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.64</v>
+      </c>
+      <c r="K13">
+        <v>0.921</v>
+      </c>
+      <c r="L13">
+        <v>1.719</v>
+      </c>
+      <c r="M13">
+        <v>0.16686021</v>
+      </c>
+      <c r="N13">
+        <v>1.55213979</v>
+      </c>
+      <c r="O13">
+        <v>0.3880349475</v>
+      </c>
+      <c r="P13">
+        <v>1.1641048425</v>
+      </c>
+      <c r="Q13">
+        <v>2.0851048425</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1744225248047917</v>
+      </c>
+      <c r="T13">
+        <v>0.8802083404389254</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.035475</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>10.30203665691179</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1591367538961199</v>
+      </c>
+      <c r="C14">
+        <v>29.88837342715413</v>
+      </c>
+      <c r="D14">
+        <v>33.09977342715413</v>
+      </c>
+      <c r="E14">
+        <v>0.4783999999999997</v>
+      </c>
+      <c r="F14">
+        <v>3.8484</v>
+      </c>
+      <c r="G14">
+        <v>0.637</v>
+      </c>
+      <c r="H14">
+        <v>28.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.64</v>
+      </c>
+      <c r="K14">
+        <v>0.921</v>
+      </c>
+      <c r="L14">
+        <v>1.719</v>
+      </c>
+      <c r="M14">
+        <v>0.19665324</v>
+      </c>
+      <c r="N14">
+        <v>1.52234676</v>
+      </c>
+      <c r="O14">
+        <v>0.38058669</v>
+      </c>
+      <c r="P14">
+        <v>1.14176007</v>
+      </c>
+      <c r="Q14">
+        <v>2.06276007</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1756110839728636</v>
+      </c>
+      <c r="T14">
+        <v>0.8879222485404583</v>
+      </c>
+      <c r="U14">
+        <v>0.0511</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.038325</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.741274743299424</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1588217107159753</v>
+      </c>
+      <c r="C15">
+        <v>29.6545565237235</v>
+      </c>
+      <c r="D15">
+        <v>33.1866565237235</v>
+      </c>
+      <c r="E15">
+        <v>0.7991000000000001</v>
+      </c>
+      <c r="F15">
+        <v>4.1691</v>
+      </c>
+      <c r="G15">
+        <v>0.637</v>
+      </c>
+      <c r="H15">
+        <v>28.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.64</v>
+      </c>
+      <c r="K15">
+        <v>0.921</v>
+      </c>
+      <c r="L15">
+        <v>1.719</v>
+      </c>
+      <c r="M15">
+        <v>0.21304101</v>
+      </c>
+      <c r="N15">
+        <v>1.50595899</v>
+      </c>
+      <c r="O15">
+        <v>0.3764897475</v>
+      </c>
+      <c r="P15">
+        <v>1.1294692425</v>
+      </c>
+      <c r="Q15">
+        <v>2.0504692425</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1768269663402015</v>
+      </c>
+      <c r="T15">
+        <v>0.8958134878627162</v>
+      </c>
+      <c r="U15">
+        <v>0.0511</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.038325</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>8.068868993814853</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1587061675358307</v>
+      </c>
+      <c r="C16">
+        <v>29.3658356279841</v>
+      </c>
+      <c r="D16">
+        <v>33.21863562798411</v>
+      </c>
+      <c r="E16">
+        <v>1.119800000000001</v>
+      </c>
+      <c r="F16">
+        <v>4.489800000000001</v>
+      </c>
+      <c r="G16">
+        <v>0.637</v>
+      </c>
+      <c r="H16">
+        <v>28.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.64</v>
+      </c>
+      <c r="K16">
+        <v>0.921</v>
+      </c>
+      <c r="L16">
+        <v>1.719</v>
+      </c>
+      <c r="M16">
+        <v>0.2379594000000001</v>
+      </c>
+      <c r="N16">
+        <v>1.4810406</v>
+      </c>
+      <c r="O16">
+        <v>0.37026015</v>
+      </c>
+      <c r="P16">
+        <v>1.11078045</v>
+      </c>
+      <c r="Q16">
+        <v>2.03178045</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1780711250416636</v>
+      </c>
+      <c r="T16">
+        <v>0.903888244378515</v>
+      </c>
+      <c r="U16">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>7.223921391632352</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1584053743556861</v>
+      </c>
+      <c r="C17">
+        <v>29.12867651487513</v>
+      </c>
+      <c r="D17">
+        <v>33.30217651487514</v>
+      </c>
+      <c r="E17">
+        <v>1.4405</v>
+      </c>
+      <c r="F17">
+        <v>4.8105</v>
+      </c>
+      <c r="G17">
+        <v>0.637</v>
+      </c>
+      <c r="H17">
+        <v>28.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.64</v>
+      </c>
+      <c r="K17">
+        <v>0.921</v>
+      </c>
+      <c r="L17">
+        <v>1.719</v>
+      </c>
+      <c r="M17">
+        <v>0.2549565</v>
+      </c>
+      <c r="N17">
+        <v>1.4640435</v>
+      </c>
+      <c r="O17">
+        <v>0.366010875</v>
+      </c>
+      <c r="P17">
+        <v>1.098032625</v>
+      </c>
+      <c r="Q17">
+        <v>2.019032625</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.179344558065513</v>
+      </c>
+      <c r="T17">
+        <v>0.9121529951652737</v>
+      </c>
+      <c r="U17">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.742326632190196</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1581045811755414</v>
+      </c>
+      <c r="C18">
+        <v>28.89193865179349</v>
+      </c>
+      <c r="D18">
+        <v>33.38613865179349</v>
+      </c>
+      <c r="E18">
+        <v>1.7612</v>
+      </c>
+      <c r="F18">
+        <v>5.1312</v>
+      </c>
+      <c r="G18">
+        <v>0.637</v>
+      </c>
+      <c r="H18">
+        <v>28.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.64</v>
+      </c>
+      <c r="K18">
+        <v>0.921</v>
+      </c>
+      <c r="L18">
+        <v>1.719</v>
+      </c>
+      <c r="M18">
+        <v>0.2719536</v>
+      </c>
+      <c r="N18">
+        <v>1.4470464</v>
+      </c>
+      <c r="O18">
+        <v>0.3617616</v>
+      </c>
+      <c r="P18">
+        <v>1.0852848</v>
+      </c>
+      <c r="Q18">
+        <v>2.0062848</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1806483109232636</v>
+      </c>
+      <c r="T18">
+        <v>0.9206145257326696</v>
+      </c>
+      <c r="U18">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.03975000000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>6.32093121767831</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1580587879953968</v>
+      </c>
+      <c r="C19">
+        <v>28.58405831470734</v>
+      </c>
+      <c r="D19">
+        <v>33.39895831470734</v>
+      </c>
+      <c r="E19">
+        <v>2.0819</v>
+      </c>
+      <c r="F19">
+        <v>5.4519</v>
+      </c>
+      <c r="G19">
+        <v>0.637</v>
+      </c>
+      <c r="H19">
+        <v>28.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.64</v>
+      </c>
+      <c r="K19">
+        <v>0.921</v>
+      </c>
+      <c r="L19">
+        <v>1.719</v>
+      </c>
+      <c r="M19">
+        <v>0.2998545</v>
+      </c>
+      <c r="N19">
+        <v>1.4191455</v>
+      </c>
+      <c r="O19">
+        <v>0.354786375</v>
+      </c>
+      <c r="P19">
+        <v>1.064359125</v>
+      </c>
+      <c r="Q19">
+        <v>1.985359125</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1819834795125262</v>
+      </c>
+      <c r="T19">
+        <v>0.9292799486028943</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.04125</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.732780398493269</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1577729948152521</v>
+      </c>
+      <c r="C20">
+        <v>28.34358824020515</v>
+      </c>
+      <c r="D20">
+        <v>33.47918824020515</v>
+      </c>
+      <c r="E20">
+        <v>2.4026</v>
+      </c>
+      <c r="F20">
+        <v>5.7726</v>
+      </c>
+      <c r="G20">
+        <v>0.637</v>
+      </c>
+      <c r="H20">
+        <v>28.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.64</v>
+      </c>
+      <c r="K20">
+        <v>0.921</v>
+      </c>
+      <c r="L20">
+        <v>1.719</v>
+      </c>
+      <c r="M20">
+        <v>0.317493</v>
+      </c>
+      <c r="N20">
+        <v>1.401507</v>
+      </c>
+      <c r="O20">
+        <v>0.35037675</v>
+      </c>
+      <c r="P20">
+        <v>1.05113025</v>
+      </c>
+      <c r="Q20">
+        <v>1.97213025</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1833512131893318</v>
+      </c>
+      <c r="T20">
+        <v>0.9381567232504414</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.04125</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.414292598576977</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1574872016351075</v>
+      </c>
+      <c r="C21">
+        <v>28.1035045454513</v>
+      </c>
+      <c r="D21">
+        <v>33.5598045454513</v>
+      </c>
+      <c r="E21">
+        <v>2.7233</v>
+      </c>
+      <c r="F21">
+        <v>6.0933</v>
+      </c>
+      <c r="G21">
+        <v>0.637</v>
+      </c>
+      <c r="H21">
+        <v>28.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.64</v>
+      </c>
+      <c r="K21">
+        <v>0.921</v>
+      </c>
+      <c r="L21">
+        <v>1.719</v>
+      </c>
+      <c r="M21">
+        <v>0.3351315</v>
+      </c>
+      <c r="N21">
+        <v>1.3838685</v>
+      </c>
+      <c r="O21">
+        <v>0.345967125</v>
+      </c>
+      <c r="P21">
+        <v>1.037901375</v>
+      </c>
+      <c r="Q21">
+        <v>1.958901375</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1847527180680339</v>
+      </c>
+      <c r="T21">
+        <v>0.9472526775189158</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.04125</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.12932983023082</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1572014084549629</v>
+      </c>
+      <c r="C22">
+        <v>27.86381002833562</v>
+      </c>
+      <c r="D22">
+        <v>33.64081002833562</v>
+      </c>
+      <c r="E22">
+        <v>3.044</v>
+      </c>
+      <c r="F22">
+        <v>6.414000000000001</v>
+      </c>
+      <c r="G22">
+        <v>0.637</v>
+      </c>
+      <c r="H22">
+        <v>28.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.64</v>
+      </c>
+      <c r="K22">
+        <v>0.921</v>
+      </c>
+      <c r="L22">
+        <v>1.719</v>
+      </c>
+      <c r="M22">
+        <v>0.35277</v>
+      </c>
+      <c r="N22">
+        <v>1.36623</v>
+      </c>
+      <c r="O22">
+        <v>0.3415575</v>
+      </c>
+      <c r="P22">
+        <v>1.0246725</v>
+      </c>
+      <c r="Q22">
+        <v>1.9456725</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1861892605687036</v>
+      </c>
+      <c r="T22">
+        <v>0.956576030644102</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.04125</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.872863338719279</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1569156152748182</v>
+      </c>
+      <c r="C23">
+        <v>27.62450751382702</v>
+      </c>
+      <c r="D23">
+        <v>33.72220751382702</v>
+      </c>
+      <c r="E23">
+        <v>3.3647</v>
+      </c>
+      <c r="F23">
+        <v>6.7347</v>
+      </c>
+      <c r="G23">
+        <v>0.637</v>
+      </c>
+      <c r="H23">
+        <v>28.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.64</v>
+      </c>
+      <c r="K23">
+        <v>0.921</v>
+      </c>
+      <c r="L23">
+        <v>1.719</v>
+      </c>
+      <c r="M23">
+        <v>0.3704085</v>
+      </c>
+      <c r="N23">
+        <v>1.3485915</v>
+      </c>
+      <c r="O23">
+        <v>0.337147875</v>
+      </c>
+      <c r="P23">
+        <v>1.011443625</v>
+      </c>
+      <c r="Q23">
+        <v>1.932443625</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1876621712339471</v>
+      </c>
+      <c r="T23">
+        <v>0.966135418025622</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.04125</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.640822227351694</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1572568220946736</v>
+      </c>
+      <c r="C24">
+        <v>27.20667298851367</v>
+      </c>
+      <c r="D24">
+        <v>33.62507298851366</v>
+      </c>
+      <c r="E24">
+        <v>3.6854</v>
+      </c>
+      <c r="F24">
+        <v>7.0554</v>
+      </c>
+      <c r="G24">
+        <v>0.637</v>
+      </c>
+      <c r="H24">
+        <v>28.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.64</v>
+      </c>
+      <c r="K24">
+        <v>0.921</v>
+      </c>
+      <c r="L24">
+        <v>1.719</v>
+      </c>
+      <c r="M24">
+        <v>0.41485752</v>
+      </c>
+      <c r="N24">
+        <v>1.30414248</v>
+      </c>
+      <c r="O24">
+        <v>0.32603562</v>
+      </c>
+      <c r="P24">
+        <v>0.97810686</v>
+      </c>
+      <c r="Q24">
+        <v>1.89910686</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1891728488393251</v>
+      </c>
+      <c r="T24">
+        <v>0.9759399179041039</v>
+      </c>
+      <c r="U24">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.0441</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.143591274421155</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1577240289145289</v>
+      </c>
+      <c r="C25">
+        <v>26.75387299525109</v>
+      </c>
+      <c r="D25">
+        <v>33.49297299525109</v>
+      </c>
+      <c r="E25">
+        <v>4.0061</v>
+      </c>
+      <c r="F25">
+        <v>7.3761</v>
+      </c>
+      <c r="G25">
+        <v>0.637</v>
+      </c>
+      <c r="H25">
+        <v>28.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.64</v>
+      </c>
+      <c r="K25">
+        <v>0.921</v>
+      </c>
+      <c r="L25">
+        <v>1.719</v>
+      </c>
+      <c r="M25">
+        <v>0.4646943</v>
+      </c>
+      <c r="N25">
+        <v>1.2543057</v>
+      </c>
+      <c r="O25">
+        <v>0.313576425</v>
+      </c>
+      <c r="P25">
+        <v>0.9407292750000001</v>
+      </c>
+      <c r="Q25">
+        <v>1.861729275</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1907227648240636</v>
+      </c>
+      <c r="T25">
+        <v>0.9859990801170921</v>
+      </c>
+      <c r="U25">
+        <v>0.063</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.04725</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.699206123251351</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1574982357343843</v>
+      </c>
+      <c r="C26">
+        <v>26.49688485110393</v>
+      </c>
+      <c r="D26">
+        <v>33.55668485110393</v>
+      </c>
+      <c r="E26">
+        <v>4.3268</v>
+      </c>
+      <c r="F26">
+        <v>7.6968</v>
+      </c>
+      <c r="G26">
+        <v>0.637</v>
+      </c>
+      <c r="H26">
+        <v>28.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.64</v>
+      </c>
+      <c r="K26">
+        <v>0.921</v>
+      </c>
+      <c r="L26">
+        <v>1.719</v>
+      </c>
+      <c r="M26">
+        <v>0.4848984</v>
+      </c>
+      <c r="N26">
+        <v>1.2341016</v>
+      </c>
+      <c r="O26">
+        <v>0.3085254</v>
+      </c>
+      <c r="P26">
+        <v>0.9255762000000001</v>
+      </c>
+      <c r="Q26">
+        <v>1.8465762</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1923134680715583</v>
+      </c>
+      <c r="T26">
+        <v>0.9963229571251589</v>
+      </c>
+      <c r="U26">
+        <v>0.063</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.04725</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.545072534782544</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1586036925542397</v>
+      </c>
+      <c r="C27">
+        <v>25.86654943562126</v>
+      </c>
+      <c r="D27">
+        <v>33.24704943562126</v>
+      </c>
+      <c r="E27">
+        <v>4.6475</v>
+      </c>
+      <c r="F27">
+        <v>8.0175</v>
+      </c>
+      <c r="G27">
+        <v>0.637</v>
+      </c>
+      <c r="H27">
+        <v>28.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.64</v>
+      </c>
+      <c r="K27">
+        <v>0.921</v>
+      </c>
+      <c r="L27">
+        <v>1.719</v>
+      </c>
+      <c r="M27">
+        <v>0.56202675</v>
+      </c>
+      <c r="N27">
+        <v>1.15697325</v>
+      </c>
+      <c r="O27">
+        <v>0.2892433125</v>
+      </c>
+      <c r="P27">
+        <v>0.8677299375</v>
+      </c>
+      <c r="Q27">
+        <v>1.7887299375</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1939465900723195</v>
+      </c>
+      <c r="T27">
+        <v>1.006922137520107</v>
+      </c>
+      <c r="U27">
+        <v>0.0701</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.052575</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>3.058573279652614</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.162584649374095</v>
+      </c>
+      <c r="C28">
+        <v>24.47661291186775</v>
+      </c>
+      <c r="D28">
+        <v>32.17781291186775</v>
+      </c>
+      <c r="E28">
+        <v>4.9682</v>
+      </c>
+      <c r="F28">
+        <v>8.338200000000001</v>
+      </c>
+      <c r="G28">
+        <v>0.637</v>
+      </c>
+      <c r="H28">
+        <v>28.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.64</v>
+      </c>
+      <c r="K28">
+        <v>0.921</v>
+      </c>
+      <c r="L28">
+        <v>1.719</v>
+      </c>
+      <c r="M28">
+        <v>0.7621114800000002</v>
+      </c>
+      <c r="N28">
+        <v>0.9568885199999999</v>
+      </c>
+      <c r="O28">
+        <v>0.23922213</v>
+      </c>
+      <c r="P28">
+        <v>0.71766639</v>
+      </c>
+      <c r="Q28">
+        <v>1.63866639</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1956238505055338</v>
+      </c>
+      <c r="T28">
+        <v>1.017807782250054</v>
+      </c>
+      <c r="U28">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.06855</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.255575522888068</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1625718561939504</v>
+      </c>
+      <c r="C29">
+        <v>24.1592388420905</v>
+      </c>
+      <c r="D29">
+        <v>32.1811388420905</v>
+      </c>
+      <c r="E29">
+        <v>5.288900000000001</v>
+      </c>
+      <c r="F29">
+        <v>8.658900000000001</v>
+      </c>
+      <c r="G29">
+        <v>0.637</v>
+      </c>
+      <c r="H29">
+        <v>28.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.64</v>
+      </c>
+      <c r="K29">
+        <v>0.921</v>
+      </c>
+      <c r="L29">
+        <v>1.719</v>
+      </c>
+      <c r="M29">
+        <v>0.7914234600000002</v>
+      </c>
+      <c r="N29">
+        <v>0.9275765399999999</v>
+      </c>
+      <c r="O29">
+        <v>0.231894135</v>
+      </c>
+      <c r="P29">
+        <v>0.6956824049999999</v>
+      </c>
+      <c r="Q29">
+        <v>1.616682405</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1973470632793841</v>
+      </c>
+      <c r="T29">
+        <v>1.028991663821918</v>
+      </c>
+      <c r="U29">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.06855</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.172035688707029</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1625590630138057</v>
+      </c>
+      <c r="C30">
+        <v>23.84186545992713</v>
+      </c>
+      <c r="D30">
+        <v>32.18446545992713</v>
+      </c>
+      <c r="E30">
+        <v>5.609600000000001</v>
+      </c>
+      <c r="F30">
+        <v>8.979600000000001</v>
+      </c>
+      <c r="G30">
+        <v>0.637</v>
+      </c>
+      <c r="H30">
+        <v>28.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.64</v>
+      </c>
+      <c r="K30">
+        <v>0.921</v>
+      </c>
+      <c r="L30">
+        <v>1.719</v>
+      </c>
+      <c r="M30">
+        <v>0.8207354400000002</v>
+      </c>
+      <c r="N30">
+        <v>0.8982645599999999</v>
+      </c>
+      <c r="O30">
+        <v>0.22456614</v>
+      </c>
+      <c r="P30">
+        <v>0.6736984199999999</v>
+      </c>
+      <c r="Q30">
+        <v>1.59469842</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1991181430747302</v>
+      </c>
+      <c r="T30">
+        <v>1.040486208770778</v>
+      </c>
+      <c r="U30">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.06855</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.094462985538921</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1625462698336611</v>
+      </c>
+      <c r="C31">
+        <v>23.52449276559091</v>
+      </c>
+      <c r="D31">
+        <v>32.18779276559091</v>
+      </c>
+      <c r="E31">
+        <v>5.9303</v>
+      </c>
+      <c r="F31">
+        <v>9.3003</v>
+      </c>
+      <c r="G31">
+        <v>0.637</v>
+      </c>
+      <c r="H31">
+        <v>28.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.64</v>
+      </c>
+      <c r="K31">
+        <v>0.921</v>
+      </c>
+      <c r="L31">
+        <v>1.719</v>
+      </c>
+      <c r="M31">
+        <v>0.8500474200000001</v>
+      </c>
+      <c r="N31">
+        <v>0.86895258</v>
+      </c>
+      <c r="O31">
+        <v>0.217238145</v>
+      </c>
+      <c r="P31">
+        <v>0.6517144349999999</v>
+      </c>
+      <c r="Q31">
+        <v>1.572714435</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2009391124417762</v>
+      </c>
+      <c r="T31">
+        <v>1.052304543718197</v>
+      </c>
+      <c r="U31">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.06855</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>2.022240123968613</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1672809766535164</v>
+      </c>
+      <c r="C32">
+        <v>22.01762679851299</v>
+      </c>
+      <c r="D32">
+        <v>31.00162679851299</v>
+      </c>
+      <c r="E32">
+        <v>6.251</v>
+      </c>
+      <c r="F32">
+        <v>9.621</v>
+      </c>
+      <c r="G32">
+        <v>0.637</v>
+      </c>
+      <c r="H32">
+        <v>28.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.64</v>
+      </c>
+      <c r="K32">
+        <v>0.921</v>
+      </c>
+      <c r="L32">
+        <v>1.719</v>
+      </c>
+      <c r="M32">
+        <v>1.0823625</v>
+      </c>
+      <c r="N32">
+        <v>0.6366375</v>
+      </c>
+      <c r="O32">
+        <v>0.159159375</v>
+      </c>
+      <c r="P32">
+        <v>0.477478125</v>
+      </c>
+      <c r="Q32">
+        <v>1.398478125</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2028121095050235</v>
+      </c>
+      <c r="T32">
+        <v>1.064460545378399</v>
+      </c>
+      <c r="U32">
+        <v>0.1125</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>1.58819249558258</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1674264334733718</v>
+      </c>
+      <c r="C33">
+        <v>21.66186870102335</v>
+      </c>
+      <c r="D33">
+        <v>30.96656870102335</v>
+      </c>
+      <c r="E33">
+        <v>6.571700000000001</v>
+      </c>
+      <c r="F33">
+        <v>9.941700000000001</v>
+      </c>
+      <c r="G33">
+        <v>0.637</v>
+      </c>
+      <c r="H33">
+        <v>28.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.64</v>
+      </c>
+      <c r="K33">
+        <v>0.921</v>
+      </c>
+      <c r="L33">
+        <v>1.719</v>
+      </c>
+      <c r="M33">
+        <v>1.11844125</v>
+      </c>
+      <c r="N33">
+        <v>0.60055875</v>
+      </c>
+      <c r="O33">
+        <v>0.1501396875</v>
+      </c>
+      <c r="P33">
+        <v>0.4504190625</v>
+      </c>
+      <c r="Q33">
+        <v>1.3714190625</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.20473939633822</v>
+      </c>
+      <c r="T33">
+        <v>1.07696889491281</v>
+      </c>
+      <c r="U33">
+        <v>0.1125</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.08437500000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>1.536960479596045</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1915529900027277</v>
+      </c>
+      <c r="C34">
+        <v>16.45015694228736</v>
+      </c>
+      <c r="D34">
+        <v>26.07555694228736</v>
+      </c>
+      <c r="E34">
+        <v>6.892399999999999</v>
+      </c>
+      <c r="F34">
+        <v>10.2624</v>
+      </c>
+      <c r="G34">
+        <v>0.637</v>
+      </c>
+      <c r="H34">
+        <v>28.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.64</v>
+      </c>
+      <c r="K34">
+        <v>0.921</v>
+      </c>
+      <c r="L34">
+        <v>1.719</v>
+      </c>
+      <c r="M34">
+        <v>2.01758784</v>
+      </c>
+      <c r="N34">
+        <v>-0.2985878399999999</v>
+      </c>
+      <c r="O34">
+        <v>-0.07464695999999998</v>
+      </c>
+      <c r="P34">
+        <v>-0.22394088</v>
+      </c>
+      <c r="Q34">
+        <v>0.69705912</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2088843590944202</v>
+      </c>
+      <c r="T34">
+        <v>1.103870258046018</v>
+      </c>
+      <c r="U34">
+        <v>0.1966</v>
+      </c>
+      <c r="V34">
+        <v>0.2130018785204415</v>
+      </c>
+      <c r="W34">
+        <v>0.1547238306828812</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.8520075140817661</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1931309900027277</v>
+      </c>
+      <c r="C35">
+        <v>15.86284018013088</v>
+      </c>
+      <c r="D35">
+        <v>25.80894018013088</v>
+      </c>
+      <c r="E35">
+        <v>7.2131</v>
+      </c>
+      <c r="F35">
+        <v>10.5831</v>
+      </c>
+      <c r="G35">
+        <v>0.637</v>
+      </c>
+      <c r="H35">
+        <v>28.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.64</v>
+      </c>
+      <c r="K35">
+        <v>0.921</v>
+      </c>
+      <c r="L35">
+        <v>1.719</v>
+      </c>
+      <c r="M35">
+        <v>2.08063746</v>
+      </c>
+      <c r="N35">
+        <v>-0.3616374600000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.09040936500000002</v>
+      </c>
+      <c r="P35">
+        <v>-0.2712280950000001</v>
+      </c>
+      <c r="Q35">
+        <v>0.6497719049999999</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2114229316182175</v>
+      </c>
+      <c r="T35">
+        <v>1.120345933539242</v>
+      </c>
+      <c r="U35">
+        <v>0.1966</v>
+      </c>
+      <c r="V35">
+        <v>0.2065472761410342</v>
+      </c>
+      <c r="W35">
+        <v>0.1559928055106727</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.8261891045641367</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1947089900027277</v>
+      </c>
+      <c r="C36">
+        <v>15.28092042876482</v>
+      </c>
+      <c r="D36">
+        <v>25.54772042876482</v>
+      </c>
+      <c r="E36">
+        <v>7.5338</v>
+      </c>
+      <c r="F36">
+        <v>10.9038</v>
+      </c>
+      <c r="G36">
+        <v>0.637</v>
+      </c>
+      <c r="H36">
+        <v>28.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.64</v>
+      </c>
+      <c r="K36">
+        <v>0.921</v>
+      </c>
+      <c r="L36">
+        <v>1.719</v>
+      </c>
+      <c r="M36">
+        <v>2.14368708</v>
+      </c>
+      <c r="N36">
+        <v>-0.4246870799999998</v>
+      </c>
+      <c r="O36">
+        <v>-0.1061717699999999</v>
+      </c>
+      <c r="P36">
+        <v>-0.3185153099999998</v>
+      </c>
+      <c r="Q36">
+        <v>0.6024846900000003</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2140384305821299</v>
+      </c>
+      <c r="T36">
+        <v>1.1373208719262</v>
+      </c>
+      <c r="U36">
+        <v>0.1966</v>
+      </c>
+      <c r="V36">
+        <v>0.2004723562545332</v>
+      </c>
+      <c r="W36">
+        <v>0.1571871347603588</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.8018894250181329</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2029875812816181</v>
+      </c>
+      <c r="C37">
+        <v>13.6720649307291</v>
+      </c>
+      <c r="D37">
+        <v>24.2595649307291</v>
+      </c>
+      <c r="E37">
+        <v>7.854500000000001</v>
+      </c>
+      <c r="F37">
+        <v>11.2245</v>
+      </c>
+      <c r="G37">
+        <v>0.637</v>
+      </c>
+      <c r="H37">
+        <v>28.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.64</v>
+      </c>
+      <c r="K37">
+        <v>0.921</v>
+      </c>
+      <c r="L37">
+        <v>1.719</v>
+      </c>
+      <c r="M37">
+        <v>2.3997981</v>
+      </c>
+      <c r="N37">
+        <v>-0.6807980999999999</v>
+      </c>
+      <c r="O37">
+        <v>-0.170199525</v>
+      </c>
+      <c r="P37">
+        <v>-0.5105985749999999</v>
+      </c>
+      <c r="Q37">
+        <v>0.4104014250000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2177814699432249</v>
+      </c>
+      <c r="T37">
+        <v>1.161613698423636</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1790775649001472</v>
+      </c>
+      <c r="W37">
+        <v>0.1755132166243485</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.716310259600589</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2047375812816182</v>
+      </c>
+      <c r="C38">
+        <v>13.09552030348504</v>
+      </c>
+      <c r="D38">
+        <v>24.00372030348504</v>
+      </c>
+      <c r="E38">
+        <v>8.1752</v>
+      </c>
+      <c r="F38">
+        <v>11.5452</v>
+      </c>
+      <c r="G38">
+        <v>0.637</v>
+      </c>
+      <c r="H38">
+        <v>28.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.64</v>
+      </c>
+      <c r="K38">
+        <v>0.921</v>
+      </c>
+      <c r="L38">
+        <v>1.719</v>
+      </c>
+      <c r="M38">
+        <v>2.46836376</v>
+      </c>
+      <c r="N38">
+        <v>-0.7493637599999998</v>
+      </c>
+      <c r="O38">
+        <v>-0.18734094</v>
+      </c>
+      <c r="P38">
+        <v>-0.5620228199999999</v>
+      </c>
+      <c r="Q38">
+        <v>0.3589771800000001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2205780554110878</v>
+      </c>
+      <c r="T38">
+        <v>1.179763912461505</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1741031880973654</v>
+      </c>
+      <c r="W38">
+        <v>0.1765767383847833</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.6964127523894614</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2064875812816181</v>
+      </c>
+      <c r="C39">
+        <v>12.52431570314405</v>
+      </c>
+      <c r="D39">
+        <v>23.75321570314405</v>
+      </c>
+      <c r="E39">
+        <v>8.495899999999999</v>
+      </c>
+      <c r="F39">
+        <v>11.8659</v>
+      </c>
+      <c r="G39">
+        <v>0.637</v>
+      </c>
+      <c r="H39">
+        <v>28.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.64</v>
+      </c>
+      <c r="K39">
+        <v>0.921</v>
+      </c>
+      <c r="L39">
+        <v>1.719</v>
+      </c>
+      <c r="M39">
+        <v>2.53692942</v>
+      </c>
+      <c r="N39">
+        <v>-0.8179294199999998</v>
+      </c>
+      <c r="O39">
+        <v>-0.2044823549999999</v>
+      </c>
+      <c r="P39">
+        <v>-0.6134470649999999</v>
+      </c>
+      <c r="Q39">
+        <v>0.3075529350000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2234634213699939</v>
+      </c>
+      <c r="T39">
+        <v>1.198490323770418</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.1693976965271663</v>
+      </c>
+      <c r="W39">
+        <v>0.1775827724824918</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.6775907861086652</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2082375812816182</v>
+      </c>
+      <c r="C40">
+        <v>11.95828566971178</v>
+      </c>
+      <c r="D40">
+        <v>23.50788566971178</v>
+      </c>
+      <c r="E40">
+        <v>8.816600000000001</v>
+      </c>
+      <c r="F40">
+        <v>12.1866</v>
+      </c>
+      <c r="G40">
+        <v>0.637</v>
+      </c>
+      <c r="H40">
+        <v>28.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.64</v>
+      </c>
+      <c r="K40">
+        <v>0.921</v>
+      </c>
+      <c r="L40">
+        <v>1.719</v>
+      </c>
+      <c r="M40">
+        <v>2.60549508</v>
+      </c>
+      <c r="N40">
+        <v>-0.8864950799999998</v>
+      </c>
+      <c r="O40">
+        <v>-0.2216237699999999</v>
+      </c>
+      <c r="P40">
+        <v>-0.6648713099999999</v>
+      </c>
+      <c r="Q40">
+        <v>0.2561286900000002</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2264418636501551</v>
+      </c>
+      <c r="T40">
+        <v>1.217820812863489</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.1649398624080304</v>
+      </c>
+      <c r="W40">
+        <v>0.1785358574171631</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.6597594496321214</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2099875812816182</v>
+      </c>
+      <c r="C41">
+        <v>11.39727150898818</v>
+      </c>
+      <c r="D41">
+        <v>23.26757150898818</v>
+      </c>
+      <c r="E41">
+        <v>9.1373</v>
+      </c>
+      <c r="F41">
+        <v>12.5073</v>
+      </c>
+      <c r="G41">
+        <v>0.637</v>
+      </c>
+      <c r="H41">
+        <v>28.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.64</v>
+      </c>
+      <c r="K41">
+        <v>0.921</v>
+      </c>
+      <c r="L41">
+        <v>1.719</v>
+      </c>
+      <c r="M41">
+        <v>2.67406074</v>
+      </c>
+      <c r="N41">
+        <v>-0.9550607399999997</v>
+      </c>
+      <c r="O41">
+        <v>-0.2387651849999999</v>
+      </c>
+      <c r="P41">
+        <v>-0.7162955549999999</v>
+      </c>
+      <c r="Q41">
+        <v>0.2047044450000002</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2295179597755675</v>
+      </c>
+      <c r="T41">
+        <v>1.237785088484202</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.1607106351667988</v>
+      </c>
+      <c r="W41">
+        <v>0.1794400662013384</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.6428425406671953</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2117375812816182</v>
+      </c>
+      <c r="C42">
+        <v>10.84112095024339</v>
+      </c>
+      <c r="D42">
+        <v>23.03212095024339</v>
+      </c>
+      <c r="E42">
+        <v>9.458000000000002</v>
+      </c>
+      <c r="F42">
+        <v>12.828</v>
+      </c>
+      <c r="G42">
+        <v>0.637</v>
+      </c>
+      <c r="H42">
+        <v>28.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.64</v>
+      </c>
+      <c r="K42">
+        <v>0.921</v>
+      </c>
+      <c r="L42">
+        <v>1.719</v>
+      </c>
+      <c r="M42">
+        <v>2.7426264</v>
+      </c>
+      <c r="N42">
+        <v>-1.0236264</v>
+      </c>
+      <c r="O42">
+        <v>-0.2559066</v>
+      </c>
+      <c r="P42">
+        <v>-0.7677198000000001</v>
+      </c>
+      <c r="Q42">
+        <v>0.1532802</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2326965924384936</v>
+      </c>
+      <c r="T42">
+        <v>1.258414839958939</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.1566928692876288</v>
+      </c>
+      <c r="W42">
+        <v>0.180299064546305</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.6267714771505153</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2134875812816182</v>
+      </c>
+      <c r="C43">
+        <v>10.28968782446986</v>
+      </c>
+      <c r="D43">
+        <v>22.80138782446986</v>
+      </c>
+      <c r="E43">
+        <v>9.778700000000001</v>
+      </c>
+      <c r="F43">
+        <v>13.1487</v>
+      </c>
+      <c r="G43">
+        <v>0.637</v>
+      </c>
+      <c r="H43">
+        <v>28.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.64</v>
+      </c>
+      <c r="K43">
+        <v>0.921</v>
+      </c>
+      <c r="L43">
+        <v>1.719</v>
+      </c>
+      <c r="M43">
+        <v>2.81119206</v>
+      </c>
+      <c r="N43">
+        <v>-1.09219206</v>
+      </c>
+      <c r="O43">
+        <v>-0.273048015</v>
+      </c>
+      <c r="P43">
+        <v>-0.819144045</v>
+      </c>
+      <c r="Q43">
+        <v>0.101855955</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.23598297536118</v>
+      </c>
+      <c r="T43">
+        <v>1.279743905042989</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.1528710919879306</v>
+      </c>
+      <c r="W43">
+        <v>0.1811161605329804</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.6114843679517222</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2152375812816182</v>
+      </c>
+      <c r="C44">
+        <v>9.742831761781986</v>
+      </c>
+      <c r="D44">
+        <v>22.57523176178199</v>
+      </c>
+      <c r="E44">
+        <v>10.0994</v>
+      </c>
+      <c r="F44">
+        <v>13.4694</v>
+      </c>
+      <c r="G44">
+        <v>0.637</v>
+      </c>
+      <c r="H44">
+        <v>28.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.64</v>
+      </c>
+      <c r="K44">
+        <v>0.921</v>
+      </c>
+      <c r="L44">
+        <v>1.719</v>
+      </c>
+      <c r="M44">
+        <v>2.87975772</v>
+      </c>
+      <c r="N44">
+        <v>-1.16075772</v>
+      </c>
+      <c r="O44">
+        <v>-0.2901894299999999</v>
+      </c>
+      <c r="P44">
+        <v>-0.8705682899999998</v>
+      </c>
+      <c r="Q44">
+        <v>0.05043171000000024</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2393826818329244</v>
+      </c>
+      <c r="T44">
+        <v>1.301808455129937</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.149231304083456</v>
+      </c>
+      <c r="W44">
+        <v>0.1818943471869571</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5969252163338241</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2169875812816182</v>
+      </c>
+      <c r="C45">
+        <v>9.200417906647042</v>
+      </c>
+      <c r="D45">
+        <v>22.35351790664704</v>
+      </c>
+      <c r="E45">
+        <v>10.4201</v>
+      </c>
+      <c r="F45">
+        <v>13.7901</v>
+      </c>
+      <c r="G45">
+        <v>0.637</v>
+      </c>
+      <c r="H45">
+        <v>28.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.64</v>
+      </c>
+      <c r="K45">
+        <v>0.921</v>
+      </c>
+      <c r="L45">
+        <v>1.719</v>
+      </c>
+      <c r="M45">
+        <v>2.94832338</v>
+      </c>
+      <c r="N45">
+        <v>-1.22932338</v>
+      </c>
+      <c r="O45">
+        <v>-0.307330845</v>
+      </c>
+      <c r="P45">
+        <v>-0.921992535</v>
+      </c>
+      <c r="Q45">
+        <v>-0.0009925349999999611</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2429016762510459</v>
+      </c>
+      <c r="T45">
+        <v>1.324647199956778</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.1457608086396547</v>
+      </c>
+      <c r="W45">
+        <v>0.1826363391128418</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.583043234558619</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2187375812816182</v>
+      </c>
+      <c r="C46">
+        <v>8.662316649733357</v>
+      </c>
+      <c r="D46">
+        <v>22.13611664973336</v>
+      </c>
+      <c r="E46">
+        <v>10.7408</v>
+      </c>
+      <c r="F46">
+        <v>14.1108</v>
+      </c>
+      <c r="G46">
+        <v>0.637</v>
+      </c>
+      <c r="H46">
+        <v>28.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.64</v>
+      </c>
+      <c r="K46">
+        <v>0.921</v>
+      </c>
+      <c r="L46">
+        <v>1.719</v>
+      </c>
+      <c r="M46">
+        <v>3.01688904</v>
+      </c>
+      <c r="N46">
+        <v>-1.29788904</v>
+      </c>
+      <c r="O46">
+        <v>-0.3244722599999999</v>
+      </c>
+      <c r="P46">
+        <v>-0.9734167799999998</v>
+      </c>
+      <c r="Q46">
+        <v>-0.05241677999999972</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2465463490412432</v>
+      </c>
+      <c r="T46">
+        <v>1.34830161424172</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.1424480629887535</v>
+      </c>
+      <c r="W46">
+        <v>0.1833446041330045</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.569792251955014</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2204875812816181</v>
+      </c>
+      <c r="C47">
+        <v>8.128403375255406</v>
+      </c>
+      <c r="D47">
+        <v>21.92290337525541</v>
+      </c>
+      <c r="E47">
+        <v>11.0615</v>
+      </c>
+      <c r="F47">
+        <v>14.4315</v>
+      </c>
+      <c r="G47">
+        <v>0.637</v>
+      </c>
+      <c r="H47">
+        <v>28.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.64</v>
+      </c>
+      <c r="K47">
+        <v>0.921</v>
+      </c>
+      <c r="L47">
+        <v>1.719</v>
+      </c>
+      <c r="M47">
+        <v>3.0854547</v>
+      </c>
+      <c r="N47">
+        <v>-1.3664547</v>
+      </c>
+      <c r="O47">
+        <v>-0.3416136749999999</v>
+      </c>
+      <c r="P47">
+        <v>-1.024841025</v>
+      </c>
+      <c r="Q47">
+        <v>-0.1038410249999997</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2503235553874475</v>
+      </c>
+      <c r="T47">
+        <v>1.372816189046115</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.1392825504778923</v>
+      </c>
+      <c r="W47">
+        <v>0.1840213907078266</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5571302019115693</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2222375812816182</v>
+      </c>
+      <c r="C48">
+        <v>7.598558222780907</v>
+      </c>
+      <c r="D48">
+        <v>21.71375822278091</v>
+      </c>
+      <c r="E48">
+        <v>11.3822</v>
+      </c>
+      <c r="F48">
+        <v>14.7522</v>
+      </c>
+      <c r="G48">
+        <v>0.637</v>
+      </c>
+      <c r="H48">
+        <v>28.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.64</v>
+      </c>
+      <c r="K48">
+        <v>0.921</v>
+      </c>
+      <c r="L48">
+        <v>1.719</v>
+      </c>
+      <c r="M48">
+        <v>3.15402036</v>
+      </c>
+      <c r="N48">
+        <v>-1.43502036</v>
+      </c>
+      <c r="O48">
+        <v>-0.35875509</v>
+      </c>
+      <c r="P48">
+        <v>-1.07626527</v>
+      </c>
+      <c r="Q48">
+        <v>-0.1552652699999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2542406582649929</v>
+      </c>
+      <c r="T48">
+        <v>1.398238711065488</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.1362546689457642</v>
+      </c>
+      <c r="W48">
+        <v>0.1846687517793956</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5450186757830568</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2239875812816182</v>
+      </c>
+      <c r="C49">
+        <v>7.072665862543307</v>
+      </c>
+      <c r="D49">
+        <v>21.50856586254331</v>
+      </c>
+      <c r="E49">
+        <v>11.7029</v>
+      </c>
+      <c r="F49">
+        <v>15.0729</v>
+      </c>
+      <c r="G49">
+        <v>0.637</v>
+      </c>
+      <c r="H49">
+        <v>28.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.64</v>
+      </c>
+      <c r="K49">
+        <v>0.921</v>
+      </c>
+      <c r="L49">
+        <v>1.719</v>
+      </c>
+      <c r="M49">
+        <v>3.22258602</v>
+      </c>
+      <c r="N49">
+        <v>-1.50358602</v>
+      </c>
+      <c r="O49">
+        <v>-0.375896505</v>
+      </c>
+      <c r="P49">
+        <v>-1.127689515</v>
+      </c>
+      <c r="Q49">
+        <v>-0.2066895149999999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2583055763454645</v>
+      </c>
+      <c r="T49">
+        <v>1.424620573538421</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.1333556334362798</v>
+      </c>
+      <c r="W49">
+        <v>0.1852885655713234</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5334225337451194</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2257375812816181</v>
+      </c>
+      <c r="C50">
+        <v>6.550615283374608</v>
+      </c>
+      <c r="D50">
+        <v>21.30721528337461</v>
+      </c>
+      <c r="E50">
+        <v>12.0236</v>
+      </c>
+      <c r="F50">
+        <v>15.3936</v>
+      </c>
+      <c r="G50">
+        <v>0.637</v>
+      </c>
+      <c r="H50">
+        <v>28.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.64</v>
+      </c>
+      <c r="K50">
+        <v>0.921</v>
+      </c>
+      <c r="L50">
+        <v>1.719</v>
+      </c>
+      <c r="M50">
+        <v>3.29115168</v>
+      </c>
+      <c r="N50">
+        <v>-1.572151679999999</v>
+      </c>
+      <c r="O50">
+        <v>-0.3930379199999999</v>
+      </c>
+      <c r="P50">
+        <v>-1.17911376</v>
+      </c>
+      <c r="Q50">
+        <v>-0.2581137599999996</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2625268374290311</v>
+      </c>
+      <c r="T50">
+        <v>1.452017123029545</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.130577391073024</v>
+      </c>
+      <c r="W50">
+        <v>0.1858825537885875</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5223095642920962</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2274875812816181</v>
+      </c>
+      <c r="C51">
+        <v>6.032299592439161</v>
+      </c>
+      <c r="D51">
+        <v>21.10959959243916</v>
+      </c>
+      <c r="E51">
+        <v>12.3443</v>
+      </c>
+      <c r="F51">
+        <v>15.7143</v>
+      </c>
+      <c r="G51">
+        <v>0.637</v>
+      </c>
+      <c r="H51">
+        <v>28.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.64</v>
+      </c>
+      <c r="K51">
+        <v>0.921</v>
+      </c>
+      <c r="L51">
+        <v>1.719</v>
+      </c>
+      <c r="M51">
+        <v>3.35971734</v>
+      </c>
+      <c r="N51">
+        <v>-1.64071734</v>
+      </c>
+      <c r="O51">
+        <v>-0.410179335</v>
+      </c>
+      <c r="P51">
+        <v>-1.230538005</v>
+      </c>
+      <c r="Q51">
+        <v>-0.3095380049999998</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2669136381629337</v>
+      </c>
+      <c r="T51">
+        <v>1.480488047010516</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0.127912546357248</v>
+      </c>
+      <c r="W51">
+        <v>0.1864522975888204</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.5116501854289921</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2292375812816181</v>
+      </c>
+      <c r="C52">
+        <v>5.517615826009468</v>
+      </c>
+      <c r="D52">
+        <v>20.91561582600947</v>
+      </c>
+      <c r="E52">
+        <v>12.665</v>
+      </c>
+      <c r="F52">
+        <v>16.035</v>
+      </c>
+      <c r="G52">
+        <v>0.637</v>
+      </c>
+      <c r="H52">
+        <v>28.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.64</v>
+      </c>
+      <c r="K52">
+        <v>0.921</v>
+      </c>
+      <c r="L52">
+        <v>1.719</v>
+      </c>
+      <c r="M52">
+        <v>3.428283</v>
+      </c>
+      <c r="N52">
+        <v>-1.709283</v>
+      </c>
+      <c r="O52">
+        <v>-0.42732075</v>
+      </c>
+      <c r="P52">
+        <v>-1.28196225</v>
+      </c>
+      <c r="Q52">
+        <v>-0.3609622499999998</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2714759109261923</v>
+      </c>
+      <c r="T52">
+        <v>1.510097807950727</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0.1253542954301031</v>
+      </c>
+      <c r="W52">
+        <v>0.186999251637044</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5014171817204123</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2445519988480712</v>
+      </c>
+      <c r="C53">
+        <v>3.640136420646112</v>
+      </c>
+      <c r="D53">
+        <v>19.35883642064611</v>
+      </c>
+      <c r="E53">
+        <v>12.9857</v>
+      </c>
+      <c r="F53">
+        <v>16.3557</v>
+      </c>
+      <c r="G53">
+        <v>0.637</v>
+      </c>
+      <c r="H53">
+        <v>28.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.64</v>
+      </c>
+      <c r="K53">
+        <v>0.921</v>
+      </c>
+      <c r="L53">
+        <v>1.719</v>
+      </c>
+      <c r="M53">
+        <v>3.90574116</v>
+      </c>
+      <c r="N53">
+        <v>-2.18674116</v>
+      </c>
+      <c r="O53">
+        <v>-0.5466852899999999</v>
+      </c>
+      <c r="P53">
+        <v>-1.64005587</v>
+      </c>
+      <c r="Q53">
+        <v>-0.7190558699999996</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2778864755705086</v>
+      </c>
+      <c r="T53">
+        <v>1.551703230611688</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.1100303328856539</v>
+      </c>
+      <c r="W53">
+        <v>0.2125247565069059</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.4401213315426157</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2465519988480712</v>
+      </c>
+      <c r="C54">
+        <v>3.133071557463222</v>
+      </c>
+      <c r="D54">
+        <v>19.17247155746322</v>
+      </c>
+      <c r="E54">
+        <v>13.3064</v>
+      </c>
+      <c r="F54">
+        <v>16.6764</v>
+      </c>
+      <c r="G54">
+        <v>0.637</v>
+      </c>
+      <c r="H54">
+        <v>28.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.64</v>
+      </c>
+      <c r="K54">
+        <v>0.921</v>
+      </c>
+      <c r="L54">
+        <v>1.719</v>
+      </c>
+      <c r="M54">
+        <v>3.98232432</v>
+      </c>
+      <c r="N54">
+        <v>-2.263324320000001</v>
+      </c>
+      <c r="O54">
+        <v>-0.5658310800000002</v>
+      </c>
+      <c r="P54">
+        <v>-1.69749324</v>
+      </c>
+      <c r="Q54">
+        <v>-0.7764932400000004</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2828674438115609</v>
+      </c>
+      <c r="T54">
+        <v>1.584030381249431</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.1079143649455452</v>
+      </c>
+      <c r="W54">
+        <v>0.2130300496510038</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.4316574597821806</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2485519988480713</v>
+      </c>
+      <c r="C55">
+        <v>2.629560698327133</v>
+      </c>
+      <c r="D55">
+        <v>18.98966069832713</v>
+      </c>
+      <c r="E55">
+        <v>13.6271</v>
+      </c>
+      <c r="F55">
+        <v>16.9971</v>
+      </c>
+      <c r="G55">
+        <v>0.637</v>
+      </c>
+      <c r="H55">
+        <v>28.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.64</v>
+      </c>
+      <c r="K55">
+        <v>0.921</v>
+      </c>
+      <c r="L55">
+        <v>1.719</v>
+      </c>
+      <c r="M55">
+        <v>4.05890748</v>
+      </c>
+      <c r="N55">
+        <v>-2.33990748</v>
+      </c>
+      <c r="O55">
+        <v>-0.58497687</v>
+      </c>
+      <c r="P55">
+        <v>-1.75493061</v>
+      </c>
+      <c r="Q55">
+        <v>-0.8339306099999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2880603681479771</v>
+      </c>
+      <c r="T55">
+        <v>1.617733155318569</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.105878244852233</v>
+      </c>
+      <c r="W55">
+        <v>0.2135162751292868</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.4235129794089321</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2505519988480712</v>
+      </c>
+      <c r="C56">
+        <v>2.129503140413814</v>
+      </c>
+      <c r="D56">
+        <v>18.81030314041382</v>
+      </c>
+      <c r="E56">
+        <v>13.9478</v>
+      </c>
+      <c r="F56">
+        <v>17.3178</v>
+      </c>
+      <c r="G56">
+        <v>0.637</v>
+      </c>
+      <c r="H56">
+        <v>28.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.64</v>
+      </c>
+      <c r="K56">
+        <v>0.921</v>
+      </c>
+      <c r="L56">
+        <v>1.719</v>
+      </c>
+      <c r="M56">
+        <v>4.13549064</v>
+      </c>
+      <c r="N56">
+        <v>-2.41649064</v>
+      </c>
+      <c r="O56">
+        <v>-0.60412266</v>
+      </c>
+      <c r="P56">
+        <v>-1.81236798</v>
+      </c>
+      <c r="Q56">
+        <v>-0.8913679800000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2934790718033679</v>
+      </c>
+      <c r="T56">
+        <v>1.652901267390711</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.1039175366142287</v>
+      </c>
+      <c r="W56">
+        <v>0.2139844922565222</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.4156701464569148</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2525519988480712</v>
+      </c>
+      <c r="C57">
+        <v>1.632801949858553</v>
+      </c>
+      <c r="D57">
+        <v>18.63430194985855</v>
+      </c>
+      <c r="E57">
+        <v>14.2685</v>
+      </c>
+      <c r="F57">
+        <v>17.6385</v>
+      </c>
+      <c r="G57">
+        <v>0.637</v>
+      </c>
+      <c r="H57">
+        <v>28.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.64</v>
+      </c>
+      <c r="K57">
+        <v>0.921</v>
+      </c>
+      <c r="L57">
+        <v>1.719</v>
+      </c>
+      <c r="M57">
+        <v>4.212073800000001</v>
+      </c>
+      <c r="N57">
+        <v>-2.4930738</v>
+      </c>
+      <c r="O57">
+        <v>-0.6232684500000001</v>
+      </c>
+      <c r="P57">
+        <v>-1.86980535</v>
+      </c>
+      <c r="Q57">
+        <v>-0.9488053500000002</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2991386067323316</v>
+      </c>
+      <c r="T57">
+        <v>1.68963240666606</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.1020281268576063</v>
+      </c>
+      <c r="W57">
+        <v>0.2144356833064036</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.4081125074304254</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2545519988480712</v>
+      </c>
+      <c r="C58">
+        <v>1.139363787066554</v>
+      </c>
+      <c r="D58">
+        <v>18.46156378706656</v>
+      </c>
+      <c r="E58">
+        <v>14.5892</v>
+      </c>
+      <c r="F58">
+        <v>17.9592</v>
+      </c>
+      <c r="G58">
+        <v>0.637</v>
+      </c>
+      <c r="H58">
+        <v>28.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.64</v>
+      </c>
+      <c r="K58">
+        <v>0.921</v>
+      </c>
+      <c r="L58">
+        <v>1.719</v>
+      </c>
+      <c r="M58">
+        <v>4.288656960000001</v>
+      </c>
+      <c r="N58">
+        <v>-2.569656960000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.6424142400000001</v>
+      </c>
+      <c r="P58">
+        <v>-1.92724272</v>
+      </c>
+      <c r="Q58">
+        <v>-1.00624272</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3050553932489755</v>
+      </c>
+      <c r="T58">
+        <v>1.728033143181198</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.1002061960208634</v>
+      </c>
+      <c r="W58">
+        <v>0.2148707603902179</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.4008247840834535</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2565519988480712</v>
+      </c>
+      <c r="C59">
+        <v>0.6490987416503913</v>
+      </c>
+      <c r="D59">
+        <v>18.29199874165039</v>
+      </c>
+      <c r="E59">
+        <v>14.9099</v>
+      </c>
+      <c r="F59">
+        <v>18.2799</v>
+      </c>
+      <c r="G59">
+        <v>0.637</v>
+      </c>
+      <c r="H59">
+        <v>28.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.64</v>
+      </c>
+      <c r="K59">
+        <v>0.921</v>
+      </c>
+      <c r="L59">
+        <v>1.719</v>
+      </c>
+      <c r="M59">
+        <v>4.36524012</v>
+      </c>
+      <c r="N59">
+        <v>-2.64624012</v>
+      </c>
+      <c r="O59">
+        <v>-0.66156003</v>
+      </c>
+      <c r="P59">
+        <v>-1.98468009</v>
+      </c>
+      <c r="Q59">
+        <v>-1.06368009</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3112473791384866</v>
+      </c>
+      <c r="T59">
+        <v>1.768219960464482</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.09844819258190085</v>
+      </c>
+      <c r="W59">
+        <v>0.2152905716114421</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3937927703276035</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2585519988480712</v>
+      </c>
+      <c r="C60">
+        <v>0.1619201763810416</v>
+      </c>
+      <c r="D60">
+        <v>18.12552017638104</v>
+      </c>
+      <c r="E60">
+        <v>15.2306</v>
+      </c>
+      <c r="F60">
+        <v>18.6006</v>
+      </c>
+      <c r="G60">
+        <v>0.637</v>
+      </c>
+      <c r="H60">
+        <v>28.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.64</v>
+      </c>
+      <c r="K60">
+        <v>0.921</v>
+      </c>
+      <c r="L60">
+        <v>1.719</v>
+      </c>
+      <c r="M60">
+        <v>4.44182328</v>
+      </c>
+      <c r="N60">
+        <v>-2.72282328</v>
+      </c>
+      <c r="O60">
+        <v>-0.68070582</v>
+      </c>
+      <c r="P60">
+        <v>-2.04211746</v>
+      </c>
+      <c r="Q60">
+        <v>-1.12111746</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3177342214989267</v>
+      </c>
+      <c r="T60">
+        <v>1.810320435713636</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.09675080995117842</v>
+      </c>
+      <c r="W60">
+        <v>0.2156959065836586</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3870032398047137</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2605519988480712</v>
+      </c>
+      <c r="C61">
+        <v>-0.3222554204166244</v>
+      </c>
+      <c r="D61">
+        <v>17.96204457958337</v>
+      </c>
+      <c r="E61">
+        <v>15.5513</v>
+      </c>
+      <c r="F61">
+        <v>18.9213</v>
+      </c>
+      <c r="G61">
+        <v>0.637</v>
+      </c>
+      <c r="H61">
+        <v>28.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.64</v>
+      </c>
+      <c r="K61">
+        <v>0.921</v>
+      </c>
+      <c r="L61">
+        <v>1.719</v>
+      </c>
+      <c r="M61">
+        <v>4.51840644</v>
+      </c>
+      <c r="N61">
+        <v>-2.799406439999999</v>
+      </c>
+      <c r="O61">
+        <v>-0.6998516099999998</v>
+      </c>
+      <c r="P61">
+        <v>-2.09955483</v>
+      </c>
+      <c r="Q61">
+        <v>-1.17855483</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3245374951940224</v>
+      </c>
+      <c r="T61">
+        <v>1.854474592682261</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.09511096571471779</v>
+      </c>
+      <c r="W61">
+        <v>0.2160875013873254</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3804438628588712</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2625519988480712</v>
+      </c>
+      <c r="C62">
+        <v>-0.8035085745520618</v>
+      </c>
+      <c r="D62">
+        <v>17.80149142544794</v>
+      </c>
+      <c r="E62">
+        <v>15.872</v>
+      </c>
+      <c r="F62">
+        <v>19.242</v>
+      </c>
+      <c r="G62">
+        <v>0.637</v>
+      </c>
+      <c r="H62">
+        <v>28.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.64</v>
+      </c>
+      <c r="K62">
+        <v>0.921</v>
+      </c>
+      <c r="L62">
+        <v>1.719</v>
+      </c>
+      <c r="M62">
+        <v>4.594989600000001</v>
+      </c>
+      <c r="N62">
+        <v>-2.8759896</v>
+      </c>
+      <c r="O62">
+        <v>-0.7189974000000001</v>
+      </c>
+      <c r="P62">
+        <v>-2.1569922</v>
+      </c>
+      <c r="Q62">
+        <v>-1.2359922</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.331680932573873</v>
+      </c>
+      <c r="T62">
+        <v>1.900836457499318</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.09352578295280579</v>
+      </c>
+      <c r="W62">
+        <v>0.21646604303087</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.3741031318112232</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2645519988480712</v>
+      </c>
+      <c r="C63">
+        <v>-1.281916958232223</v>
+      </c>
+      <c r="D63">
+        <v>17.64378304176778</v>
+      </c>
+      <c r="E63">
+        <v>16.1927</v>
+      </c>
+      <c r="F63">
+        <v>19.5627</v>
+      </c>
+      <c r="G63">
+        <v>0.637</v>
+      </c>
+      <c r="H63">
+        <v>28.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.64</v>
+      </c>
+      <c r="K63">
+        <v>0.921</v>
+      </c>
+      <c r="L63">
+        <v>1.719</v>
+      </c>
+      <c r="M63">
+        <v>4.67157276</v>
+      </c>
+      <c r="N63">
+        <v>-2.95257276</v>
+      </c>
+      <c r="O63">
+        <v>-0.7381431899999999</v>
+      </c>
+      <c r="P63">
+        <v>-2.21442957</v>
+      </c>
+      <c r="Q63">
+        <v>-1.29342957</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3391907000757672</v>
+      </c>
+      <c r="T63">
+        <v>1.949575853845454</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.09199257339620244</v>
+      </c>
+      <c r="W63">
+        <v>0.2168321734729869</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3679702935848098</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2665519988480711</v>
+      </c>
+      <c r="C64">
+        <v>-1.757555515355818</v>
+      </c>
+      <c r="D64">
+        <v>17.48884448464418</v>
+      </c>
+      <c r="E64">
+        <v>16.5134</v>
+      </c>
+      <c r="F64">
+        <v>19.8834</v>
+      </c>
+      <c r="G64">
+        <v>0.637</v>
+      </c>
+      <c r="H64">
+        <v>28.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.64</v>
+      </c>
+      <c r="K64">
+        <v>0.921</v>
+      </c>
+      <c r="L64">
+        <v>1.719</v>
+      </c>
+      <c r="M64">
+        <v>4.74815592</v>
+      </c>
+      <c r="N64">
+        <v>-3.02915592</v>
+      </c>
+      <c r="O64">
+        <v>-0.75728898</v>
+      </c>
+      <c r="P64">
+        <v>-2.27186694</v>
+      </c>
+      <c r="Q64">
+        <v>-1.35086694</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3470957184988137</v>
+      </c>
+      <c r="T64">
+        <v>2.000880481578229</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.09050882221239272</v>
+      </c>
+      <c r="W64">
+        <v>0.2171864932556806</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3620352888495709</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2685519988480712</v>
+      </c>
+      <c r="C65">
+        <v>-2.230496580263463</v>
+      </c>
+      <c r="D65">
+        <v>17.33660341973654</v>
+      </c>
+      <c r="E65">
+        <v>16.8341</v>
+      </c>
+      <c r="F65">
+        <v>20.2041</v>
+      </c>
+      <c r="G65">
+        <v>0.637</v>
+      </c>
+      <c r="H65">
+        <v>28.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.64</v>
+      </c>
+      <c r="K65">
+        <v>0.921</v>
+      </c>
+      <c r="L65">
+        <v>1.719</v>
+      </c>
+      <c r="M65">
+        <v>4.824739080000001</v>
+      </c>
+      <c r="N65">
+        <v>-3.10573908</v>
+      </c>
+      <c r="O65">
+        <v>-0.7764347700000001</v>
+      </c>
+      <c r="P65">
+        <v>-2.32930431</v>
+      </c>
+      <c r="Q65">
+        <v>-1.40830431</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3554280352149979</v>
+      </c>
+      <c r="T65">
+        <v>2.054958332431695</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.08907217424076744</v>
+      </c>
+      <c r="W65">
+        <v>0.2175295647913048</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3562886969630698</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2705519988480712</v>
+      </c>
+      <c r="C66">
+        <v>-2.700809990338957</v>
+      </c>
+      <c r="D66">
+        <v>17.18699000966104</v>
+      </c>
+      <c r="E66">
+        <v>17.1548</v>
+      </c>
+      <c r="F66">
+        <v>20.5248</v>
+      </c>
+      <c r="G66">
+        <v>0.637</v>
+      </c>
+      <c r="H66">
+        <v>28.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.64</v>
+      </c>
+      <c r="K66">
+        <v>0.921</v>
+      </c>
+      <c r="L66">
+        <v>1.719</v>
+      </c>
+      <c r="M66">
+        <v>4.90132224</v>
+      </c>
+      <c r="N66">
+        <v>-3.18232224</v>
+      </c>
+      <c r="O66">
+        <v>-0.7955805599999999</v>
+      </c>
+      <c r="P66">
+        <v>-2.38674168</v>
+      </c>
+      <c r="Q66">
+        <v>-1.46574168</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3642232584154145</v>
+      </c>
+      <c r="T66">
+        <v>2.112040508332575</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.08768042151825546</v>
+      </c>
+      <c r="W66">
+        <v>0.2178619153414406</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3507216860730219</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2725519988480712</v>
+      </c>
+      <c r="C67">
+        <v>-3.168563192830138</v>
+      </c>
+      <c r="D67">
+        <v>17.03993680716986</v>
+      </c>
+      <c r="E67">
+        <v>17.4755</v>
+      </c>
+      <c r="F67">
+        <v>20.8455</v>
+      </c>
+      <c r="G67">
+        <v>0.637</v>
+      </c>
+      <c r="H67">
+        <v>28.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.64</v>
+      </c>
+      <c r="K67">
+        <v>0.921</v>
+      </c>
+      <c r="L67">
+        <v>1.719</v>
+      </c>
+      <c r="M67">
+        <v>4.977905400000001</v>
+      </c>
+      <c r="N67">
+        <v>-3.258905400000001</v>
+      </c>
+      <c r="O67">
+        <v>-0.8147263500000002</v>
+      </c>
+      <c r="P67">
+        <v>-2.444179050000001</v>
+      </c>
+      <c r="Q67">
+        <v>-1.523179050000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3735210657987121</v>
+      </c>
+      <c r="T67">
+        <v>2.172384522856364</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.08633149195643612</v>
+      </c>
+      <c r="W67">
+        <v>0.2181840397208031</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3453259678257445</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2745519988480712</v>
+      </c>
+      <c r="C68">
+        <v>-3.633821346232271</v>
+      </c>
+      <c r="D68">
+        <v>16.89537865376773</v>
+      </c>
+      <c r="E68">
+        <v>17.7962</v>
+      </c>
+      <c r="F68">
+        <v>21.1662</v>
+      </c>
+      <c r="G68">
+        <v>0.637</v>
+      </c>
+      <c r="H68">
+        <v>28.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.64</v>
+      </c>
+      <c r="K68">
+        <v>0.921</v>
+      </c>
+      <c r="L68">
+        <v>1.719</v>
+      </c>
+      <c r="M68">
+        <v>5.05448856</v>
+      </c>
+      <c r="N68">
+        <v>-3.33548856</v>
+      </c>
+      <c r="O68">
+        <v>-0.83387214</v>
+      </c>
+      <c r="P68">
+        <v>-2.50161642</v>
+      </c>
+      <c r="Q68">
+        <v>-1.58061642</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.3833658030280859</v>
+      </c>
+      <c r="T68">
+        <v>2.236278185293315</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.08502343904800529</v>
+      </c>
+      <c r="W68">
+        <v>0.2184964027553364</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3400937561920212</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2765519988480712</v>
+      </c>
+      <c r="C69">
+        <v>-4.096647416554521</v>
+      </c>
+      <c r="D69">
+        <v>16.75325258344548</v>
+      </c>
+      <c r="E69">
+        <v>18.1169</v>
+      </c>
+      <c r="F69">
+        <v>21.4869</v>
+      </c>
+      <c r="G69">
+        <v>0.637</v>
+      </c>
+      <c r="H69">
+        <v>28.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.64</v>
+      </c>
+      <c r="K69">
+        <v>0.921</v>
+      </c>
+      <c r="L69">
+        <v>1.719</v>
+      </c>
+      <c r="M69">
+        <v>5.13107172</v>
+      </c>
+      <c r="N69">
+        <v>-3.41207172</v>
+      </c>
+      <c r="O69">
+        <v>-0.85301793</v>
+      </c>
+      <c r="P69">
+        <v>-2.55905379</v>
+      </c>
+      <c r="Q69">
+        <v>-1.63805379</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.393807190998634</v>
+      </c>
+      <c r="T69">
+        <v>2.304044190908264</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.08375443249504998</v>
+      </c>
+      <c r="W69">
+        <v>0.2187994415201821</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3350177299802</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2785519988480712</v>
+      </c>
+      <c r="C70">
+        <v>-4.557102268767967</v>
+      </c>
+      <c r="D70">
+        <v>16.61349773123203</v>
+      </c>
+      <c r="E70">
+        <v>18.4376</v>
+      </c>
+      <c r="F70">
+        <v>21.8076</v>
+      </c>
+      <c r="G70">
+        <v>0.637</v>
+      </c>
+      <c r="H70">
+        <v>28.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.64</v>
+      </c>
+      <c r="K70">
+        <v>0.921</v>
+      </c>
+      <c r="L70">
+        <v>1.719</v>
+      </c>
+      <c r="M70">
+        <v>5.207654880000001</v>
+      </c>
+      <c r="N70">
+        <v>-3.48865488</v>
+      </c>
+      <c r="O70">
+        <v>-0.8721637200000001</v>
+      </c>
+      <c r="P70">
+        <v>-2.61649116</v>
+      </c>
+      <c r="Q70">
+        <v>-1.69549116</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4049011657173414</v>
+      </c>
+      <c r="T70">
+        <v>2.376045571874148</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.08252274966424042</v>
+      </c>
+      <c r="W70">
+        <v>0.2190935673801794</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3300909986569617</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2805519988480712</v>
+      </c>
+      <c r="C71">
+        <v>-5.015244753714473</v>
+      </c>
+      <c r="D71">
+        <v>16.47605524628553</v>
+      </c>
+      <c r="E71">
+        <v>18.7583</v>
+      </c>
+      <c r="F71">
+        <v>22.1283</v>
+      </c>
+      <c r="G71">
+        <v>0.637</v>
+      </c>
+      <c r="H71">
+        <v>28.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.64</v>
+      </c>
+      <c r="K71">
+        <v>0.921</v>
+      </c>
+      <c r="L71">
+        <v>1.719</v>
+      </c>
+      <c r="M71">
+        <v>5.284238040000001</v>
+      </c>
+      <c r="N71">
+        <v>-3.565238040000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.8913095100000001</v>
+      </c>
+      <c r="P71">
+        <v>-2.67392853</v>
+      </c>
+      <c r="Q71">
+        <v>-1.75292853</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4167108807404814</v>
+      </c>
+      <c r="T71">
+        <v>2.452692203224927</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.08132676778504852</v>
+      </c>
+      <c r="W71">
+        <v>0.2193791678529304</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3253070711401941</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2825519988480713</v>
+      </c>
+      <c r="C72">
+        <v>-5.471131790736926</v>
+      </c>
+      <c r="D72">
+        <v>16.34086820926307</v>
+      </c>
+      <c r="E72">
+        <v>19.079</v>
+      </c>
+      <c r="F72">
+        <v>22.449</v>
+      </c>
+      <c r="G72">
+        <v>0.637</v>
+      </c>
+      <c r="H72">
+        <v>28.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.64</v>
+      </c>
+      <c r="K72">
+        <v>0.921</v>
+      </c>
+      <c r="L72">
+        <v>1.719</v>
+      </c>
+      <c r="M72">
+        <v>5.360821200000001</v>
+      </c>
+      <c r="N72">
+        <v>-3.641821200000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.9104553000000002</v>
+      </c>
+      <c r="P72">
+        <v>-2.731365900000001</v>
+      </c>
+      <c r="Q72">
+        <v>-1.810365900000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4293079100984974</v>
+      </c>
+      <c r="T72">
+        <v>2.534448609999091</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.08016495681669068</v>
+      </c>
+      <c r="W72">
+        <v>0.2196566083121743</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3206598272667628</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2845519988480712</v>
+      </c>
+      <c r="C73">
+        <v>-5.924818446274688</v>
+      </c>
+      <c r="D73">
+        <v>16.20788155372531</v>
+      </c>
+      <c r="E73">
+        <v>19.3997</v>
+      </c>
+      <c r="F73">
+        <v>22.7697</v>
+      </c>
+      <c r="G73">
+        <v>0.637</v>
+      </c>
+      <c r="H73">
+        <v>28.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.64</v>
+      </c>
+      <c r="K73">
+        <v>0.921</v>
+      </c>
+      <c r="L73">
+        <v>1.719</v>
+      </c>
+      <c r="M73">
+        <v>5.43740436</v>
+      </c>
+      <c r="N73">
+        <v>-3.71840436</v>
+      </c>
+      <c r="O73">
+        <v>-0.92960109</v>
+      </c>
+      <c r="P73">
+        <v>-2.78880327</v>
+      </c>
+      <c r="Q73">
+        <v>-1.86780327</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4427737001018938</v>
+      </c>
+      <c r="T73">
+        <v>2.621843389654231</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.07903587291786407</v>
+      </c>
+      <c r="W73">
+        <v>0.2199262335472141</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3161434916714563</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2865519988480712</v>
+      </c>
+      <c r="C74">
+        <v>-6.376358008652261</v>
+      </c>
+      <c r="D74">
+        <v>16.07704199134774</v>
+      </c>
+      <c r="E74">
+        <v>19.7204</v>
+      </c>
+      <c r="F74">
+        <v>23.0904</v>
+      </c>
+      <c r="G74">
+        <v>0.637</v>
+      </c>
+      <c r="H74">
+        <v>28.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.64</v>
+      </c>
+      <c r="K74">
+        <v>0.921</v>
+      </c>
+      <c r="L74">
+        <v>1.719</v>
+      </c>
+      <c r="M74">
+        <v>5.51398752</v>
+      </c>
+      <c r="N74">
+        <v>-3.794987519999999</v>
+      </c>
+      <c r="O74">
+        <v>-0.9487468799999998</v>
+      </c>
+      <c r="P74">
+        <v>-2.84624064</v>
+      </c>
+      <c r="Q74">
+        <v>-1.92524064</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.45720133224839</v>
+      </c>
+      <c r="T74">
+        <v>2.715480653570454</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.07793815246067153</v>
+      </c>
+      <c r="W74">
+        <v>0.2201883691923917</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3117526098426862</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2885519988480711</v>
+      </c>
+      <c r="C75">
+        <v>-6.825802059274473</v>
+      </c>
+      <c r="D75">
+        <v>15.94829794072553</v>
+      </c>
+      <c r="E75">
+        <v>20.0411</v>
+      </c>
+      <c r="F75">
+        <v>23.4111</v>
+      </c>
+      <c r="G75">
+        <v>0.637</v>
+      </c>
+      <c r="H75">
+        <v>28.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.64</v>
+      </c>
+      <c r="K75">
+        <v>0.921</v>
+      </c>
+      <c r="L75">
+        <v>1.719</v>
+      </c>
+      <c r="M75">
+        <v>5.590570680000001</v>
+      </c>
+      <c r="N75">
+        <v>-3.87157068</v>
+      </c>
+      <c r="O75">
+        <v>-0.9678926700000001</v>
+      </c>
+      <c r="P75">
+        <v>-2.90367801</v>
+      </c>
+      <c r="Q75">
+        <v>-1.98267801</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4726976778872192</v>
+      </c>
+      <c r="T75">
+        <v>2.8160540111101</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.07687050653655271</v>
+      </c>
+      <c r="W75">
+        <v>0.2204433230390712</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3074820261462109</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2905519988480712</v>
+      </c>
+      <c r="C76">
+        <v>-7.273200540428149</v>
+      </c>
+      <c r="D76">
+        <v>15.82159945957185</v>
+      </c>
+      <c r="E76">
+        <v>20.3618</v>
+      </c>
+      <c r="F76">
+        <v>23.7318</v>
+      </c>
+      <c r="G76">
+        <v>0.637</v>
+      </c>
+      <c r="H76">
+        <v>28.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.64</v>
+      </c>
+      <c r="K76">
+        <v>0.921</v>
+      </c>
+      <c r="L76">
+        <v>1.719</v>
+      </c>
+      <c r="M76">
+        <v>5.66715384</v>
+      </c>
+      <c r="N76">
+        <v>-3.94815384</v>
+      </c>
+      <c r="O76">
+        <v>-0.98703846</v>
+      </c>
+      <c r="P76">
+        <v>-2.96111538</v>
+      </c>
+      <c r="Q76">
+        <v>-2.04011538</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.4893860501136508</v>
+      </c>
+      <c r="T76">
+        <v>2.924363780768181</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0758317159076804</v>
+      </c>
+      <c r="W76">
+        <v>0.2206913862412459</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3033268636307216</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2925519988480712</v>
+      </c>
+      <c r="C77">
+        <v>-7.718601819877339</v>
+      </c>
+      <c r="D77">
+        <v>15.69689818012266</v>
+      </c>
+      <c r="E77">
+        <v>20.6825</v>
+      </c>
+      <c r="F77">
+        <v>24.0525</v>
+      </c>
+      <c r="G77">
+        <v>0.637</v>
+      </c>
+      <c r="H77">
+        <v>28.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.64</v>
+      </c>
+      <c r="K77">
+        <v>0.921</v>
+      </c>
+      <c r="L77">
+        <v>1.719</v>
+      </c>
+      <c r="M77">
+        <v>5.743737000000001</v>
+      </c>
+      <c r="N77">
+        <v>-4.024737000000001</v>
+      </c>
+      <c r="O77">
+        <v>-1.00618425</v>
+      </c>
+      <c r="P77">
+        <v>-3.01855275</v>
+      </c>
+      <c r="Q77">
+        <v>-2.09755275</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5074094921181969</v>
+      </c>
+      <c r="T77">
+        <v>3.041338331998908</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.07482062636224464</v>
+      </c>
+      <c r="W77">
+        <v>0.220932834424696</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2992825054489786</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2945519988480712</v>
+      </c>
+      <c r="C78">
+        <v>-8.162052752427794</v>
+      </c>
+      <c r="D78">
+        <v>15.57414724757221</v>
+      </c>
+      <c r="E78">
+        <v>21.0032</v>
+      </c>
+      <c r="F78">
+        <v>24.3732</v>
+      </c>
+      <c r="G78">
+        <v>0.637</v>
+      </c>
+      <c r="H78">
+        <v>28.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.64</v>
+      </c>
+      <c r="K78">
+        <v>0.921</v>
+      </c>
+      <c r="L78">
+        <v>1.719</v>
+      </c>
+      <c r="M78">
+        <v>5.820320160000001</v>
+      </c>
+      <c r="N78">
+        <v>-4.10132016</v>
+      </c>
+      <c r="O78">
+        <v>-1.02533004</v>
+      </c>
+      <c r="P78">
+        <v>-3.07599012</v>
+      </c>
+      <c r="Q78">
+        <v>-2.15499012</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5269348876231217</v>
+      </c>
+      <c r="T78">
+        <v>3.168060762498863</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.07383614443642564</v>
+      </c>
+      <c r="W78">
+        <v>0.2211679287085816</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2953445777457026</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2965519988480712</v>
+      </c>
+      <c r="C79">
+        <v>-8.603598738625191</v>
+      </c>
+      <c r="D79">
+        <v>15.45330126137481</v>
+      </c>
+      <c r="E79">
+        <v>21.3239</v>
+      </c>
+      <c r="F79">
+        <v>24.6939</v>
+      </c>
+      <c r="G79">
+        <v>0.637</v>
+      </c>
+      <c r="H79">
+        <v>28.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.64</v>
+      </c>
+      <c r="K79">
+        <v>0.921</v>
+      </c>
+      <c r="L79">
+        <v>1.719</v>
+      </c>
+      <c r="M79">
+        <v>5.89690332</v>
+      </c>
+      <c r="N79">
+        <v>-4.17790332</v>
+      </c>
+      <c r="O79">
+        <v>-1.04447583</v>
+      </c>
+      <c r="P79">
+        <v>-3.13342749</v>
+      </c>
+      <c r="Q79">
+        <v>-2.21242749</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5481581436067358</v>
+      </c>
+      <c r="T79">
+        <v>3.305802534781422</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.07287723346971882</v>
+      </c>
+      <c r="W79">
+        <v>0.2213969166474311</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2915089338788753</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2985519988480712</v>
+      </c>
+      <c r="C80">
+        <v>-9.043283780741563</v>
+      </c>
+      <c r="D80">
+        <v>15.33431621925844</v>
+      </c>
+      <c r="E80">
+        <v>21.6446</v>
+      </c>
+      <c r="F80">
+        <v>25.0146</v>
+      </c>
+      <c r="G80">
+        <v>0.637</v>
+      </c>
+      <c r="H80">
+        <v>28.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.64</v>
+      </c>
+      <c r="K80">
+        <v>0.921</v>
+      </c>
+      <c r="L80">
+        <v>1.719</v>
+      </c>
+      <c r="M80">
+        <v>5.973486480000001</v>
+      </c>
+      <c r="N80">
+        <v>-4.254486480000001</v>
+      </c>
+      <c r="O80">
+        <v>-1.06362162</v>
+      </c>
+      <c r="P80">
+        <v>-3.19086486</v>
+      </c>
+      <c r="Q80">
+        <v>-2.26986486</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.571310786497951</v>
+      </c>
+      <c r="T80">
+        <v>3.456066286362396</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.07194290996369677</v>
+      </c>
+      <c r="W80">
+        <v>0.2216200331006692</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2877716398547872</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3005519988480712</v>
+      </c>
+      <c r="C81">
+        <v>-9.481150536195141</v>
+      </c>
+      <c r="D81">
+        <v>15.21714946380486</v>
+      </c>
+      <c r="E81">
+        <v>21.9653</v>
+      </c>
+      <c r="F81">
+        <v>25.3353</v>
+      </c>
+      <c r="G81">
+        <v>0.637</v>
+      </c>
+      <c r="H81">
+        <v>28.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.64</v>
+      </c>
+      <c r="K81">
+        <v>0.921</v>
+      </c>
+      <c r="L81">
+        <v>1.719</v>
+      </c>
+      <c r="M81">
+        <v>6.05006964</v>
+      </c>
+      <c r="N81">
+        <v>-4.33106964</v>
+      </c>
+      <c r="O81">
+        <v>-1.08276741</v>
+      </c>
+      <c r="P81">
+        <v>-3.24830223</v>
+      </c>
+      <c r="Q81">
+        <v>-2.32730223</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.5966684429978535</v>
+      </c>
+      <c r="T81">
+        <v>3.620640871427272</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.07103224021732087</v>
+      </c>
+      <c r="W81">
+        <v>0.2218375010361038</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2841289608692835</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3025519988480712</v>
+      </c>
+      <c r="C82">
+        <v>-9.917240368539659</v>
+      </c>
+      <c r="D82">
+        <v>15.10175963146034</v>
+      </c>
+      <c r="E82">
+        <v>22.286</v>
+      </c>
+      <c r="F82">
+        <v>25.656</v>
+      </c>
+      <c r="G82">
+        <v>0.637</v>
+      </c>
+      <c r="H82">
+        <v>28.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.64</v>
+      </c>
+      <c r="K82">
+        <v>0.921</v>
+      </c>
+      <c r="L82">
+        <v>1.719</v>
+      </c>
+      <c r="M82">
+        <v>6.1266528</v>
+      </c>
+      <c r="N82">
+        <v>-4.4076528</v>
+      </c>
+      <c r="O82">
+        <v>-1.1019132</v>
+      </c>
+      <c r="P82">
+        <v>-3.3057396</v>
+      </c>
+      <c r="Q82">
+        <v>-2.3847396</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6245618651477463</v>
+      </c>
+      <c r="T82">
+        <v>3.801672914998636</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.07014433721460436</v>
+      </c>
+      <c r="W82">
+        <v>0.2220495322731525</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2805773488584175</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3045519988480712</v>
+      </c>
+      <c r="C83">
+        <v>-10.35159339615127</v>
+      </c>
+      <c r="D83">
+        <v>14.98810660384873</v>
+      </c>
+      <c r="E83">
+        <v>22.6067</v>
+      </c>
+      <c r="F83">
+        <v>25.9767</v>
+      </c>
+      <c r="G83">
+        <v>0.637</v>
+      </c>
+      <c r="H83">
+        <v>28.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.64</v>
+      </c>
+      <c r="K83">
+        <v>0.921</v>
+      </c>
+      <c r="L83">
+        <v>1.719</v>
+      </c>
+      <c r="M83">
+        <v>6.203235960000001</v>
+      </c>
+      <c r="N83">
+        <v>-4.48423596</v>
+      </c>
+      <c r="O83">
+        <v>-1.12105899</v>
+      </c>
+      <c r="P83">
+        <v>-3.36317697</v>
+      </c>
+      <c r="Q83">
+        <v>-2.44217697</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6553914369976275</v>
+      </c>
+      <c r="T83">
+        <v>4.001760963156459</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.06927835774281911</v>
+      </c>
+      <c r="W83">
+        <v>0.2222563281710148</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2771134309712765</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3065519988480713</v>
+      </c>
+      <c r="C84">
+        <v>-10.78424853873345</v>
+      </c>
+      <c r="D84">
+        <v>14.87615146126656</v>
+      </c>
+      <c r="E84">
+        <v>22.9274</v>
+      </c>
+      <c r="F84">
+        <v>26.2974</v>
+      </c>
+      <c r="G84">
+        <v>0.637</v>
+      </c>
+      <c r="H84">
+        <v>28.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.64</v>
+      </c>
+      <c r="K84">
+        <v>0.921</v>
+      </c>
+      <c r="L84">
+        <v>1.719</v>
+      </c>
+      <c r="M84">
+        <v>6.279819120000001</v>
+      </c>
+      <c r="N84">
+        <v>-4.560819120000001</v>
+      </c>
+      <c r="O84">
+        <v>-1.14020478</v>
+      </c>
+      <c r="P84">
+        <v>-3.42061434</v>
+      </c>
+      <c r="Q84">
+        <v>-2.49961434</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.6896465168308292</v>
+      </c>
+      <c r="T84">
+        <v>4.224081016665152</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.06843349972156522</v>
+      </c>
+      <c r="W84">
+        <v>0.2224580802664902</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2737339988862609</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3085519988480712</v>
+      </c>
+      <c r="C85">
+        <v>-11.21524356175305</v>
+      </c>
+      <c r="D85">
+        <v>14.76585643824695</v>
+      </c>
+      <c r="E85">
+        <v>23.2481</v>
+      </c>
+      <c r="F85">
+        <v>26.6181</v>
+      </c>
+      <c r="G85">
+        <v>0.637</v>
+      </c>
+      <c r="H85">
+        <v>28.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.64</v>
+      </c>
+      <c r="K85">
+        <v>0.921</v>
+      </c>
+      <c r="L85">
+        <v>1.719</v>
+      </c>
+      <c r="M85">
+        <v>6.356402280000001</v>
+      </c>
+      <c r="N85">
+        <v>-4.637402280000001</v>
+      </c>
+      <c r="O85">
+        <v>-1.15935057</v>
+      </c>
+      <c r="P85">
+        <v>-3.478051710000001</v>
+      </c>
+      <c r="Q85">
+        <v>-2.557051710000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.727931606056172</v>
+      </c>
+      <c r="T85">
+        <v>4.472556370586632</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.06760899972491986</v>
+      </c>
+      <c r="W85">
+        <v>0.2226549708656891</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.2704359988996795</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3105519988480712</v>
+      </c>
+      <c r="C86">
+        <v>-11.64461511891427</v>
+      </c>
+      <c r="D86">
+        <v>14.65718488108573</v>
+      </c>
+      <c r="E86">
+        <v>23.5688</v>
+      </c>
+      <c r="F86">
+        <v>26.9388</v>
+      </c>
+      <c r="G86">
+        <v>0.637</v>
+      </c>
+      <c r="H86">
+        <v>28.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.64</v>
+      </c>
+      <c r="K86">
+        <v>0.921</v>
+      </c>
+      <c r="L86">
+        <v>1.719</v>
+      </c>
+      <c r="M86">
+        <v>6.43298544</v>
+      </c>
+      <c r="N86">
+        <v>-4.71398544</v>
+      </c>
+      <c r="O86">
+        <v>-1.17849636</v>
+      </c>
+      <c r="P86">
+        <v>-3.53548908</v>
+      </c>
+      <c r="Q86">
+        <v>-2.61448908</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.7710023314346826</v>
+      </c>
+      <c r="T86">
+        <v>4.752091143748293</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.06680413068057559</v>
+      </c>
+      <c r="W86">
+        <v>0.2228471735934786</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2672165227223023</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3125519988480712</v>
+      </c>
+      <c r="C87">
+        <v>-12.07239879277062</v>
+      </c>
+      <c r="D87">
+        <v>14.55010120722938</v>
+      </c>
+      <c r="E87">
+        <v>23.8895</v>
+      </c>
+      <c r="F87">
+        <v>27.2595</v>
+      </c>
+      <c r="G87">
+        <v>0.637</v>
+      </c>
+      <c r="H87">
+        <v>28.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.64</v>
+      </c>
+      <c r="K87">
+        <v>0.921</v>
+      </c>
+      <c r="L87">
+        <v>1.719</v>
+      </c>
+      <c r="M87">
+        <v>6.5095686</v>
+      </c>
+      <c r="N87">
+        <v>-4.790568599999999</v>
+      </c>
+      <c r="O87">
+        <v>-1.19764215</v>
+      </c>
+      <c r="P87">
+        <v>-3.592926449999999</v>
+      </c>
+      <c r="Q87">
+        <v>-2.671926449999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8198158201969947</v>
+      </c>
+      <c r="T87">
+        <v>5.06889721999818</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.06601819973139235</v>
+      </c>
+      <c r="W87">
+        <v>0.2230348539041435</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2640727989255695</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3145519988480712</v>
+      </c>
+      <c r="C88">
+        <v>-12.49862913356968</v>
+      </c>
+      <c r="D88">
+        <v>14.44457086643032</v>
+      </c>
+      <c r="E88">
+        <v>24.2102</v>
+      </c>
+      <c r="F88">
+        <v>27.5802</v>
+      </c>
+      <c r="G88">
+        <v>0.637</v>
+      </c>
+      <c r="H88">
+        <v>28.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.64</v>
+      </c>
+      <c r="K88">
+        <v>0.921</v>
+      </c>
+      <c r="L88">
+        <v>1.719</v>
+      </c>
+      <c r="M88">
+        <v>6.586151760000001</v>
+      </c>
+      <c r="N88">
+        <v>-4.86715176</v>
+      </c>
+      <c r="O88">
+        <v>-1.21678794</v>
+      </c>
+      <c r="P88">
+        <v>-3.65036382</v>
+      </c>
+      <c r="Q88">
+        <v>-2.729363820000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.87560266449678</v>
+      </c>
+      <c r="T88">
+        <v>5.430961307140907</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.06525054624614358</v>
+      </c>
+      <c r="W88">
+        <v>0.2232181695564209</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2610021849845744</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3165519988480712</v>
+      </c>
+      <c r="C89">
+        <v>-12.92333969641953</v>
+      </c>
+      <c r="D89">
+        <v>14.34056030358047</v>
+      </c>
+      <c r="E89">
+        <v>24.5309</v>
+      </c>
+      <c r="F89">
+        <v>27.9009</v>
+      </c>
+      <c r="G89">
+        <v>0.637</v>
+      </c>
+      <c r="H89">
+        <v>28.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.64</v>
+      </c>
+      <c r="K89">
+        <v>0.921</v>
+      </c>
+      <c r="L89">
+        <v>1.719</v>
+      </c>
+      <c r="M89">
+        <v>6.66273492</v>
+      </c>
+      <c r="N89">
+        <v>-4.94373492</v>
+      </c>
+      <c r="O89">
+        <v>-1.23593373</v>
+      </c>
+      <c r="P89">
+        <v>-3.70780119</v>
+      </c>
+      <c r="Q89">
+        <v>-2.786801189999999</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.9399721002273016</v>
+      </c>
+      <c r="T89">
+        <v>5.848727561536362</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.06450053996745228</v>
+      </c>
+      <c r="W89">
+        <v>0.2233972710557724</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.2580021598698092</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3185519988480712</v>
+      </c>
+      <c r="C90">
+        <v>-13.346563076861</v>
+      </c>
+      <c r="D90">
+        <v>14.238036923139</v>
+      </c>
+      <c r="E90">
+        <v>24.8516</v>
+      </c>
+      <c r="F90">
+        <v>28.2216</v>
+      </c>
+      <c r="G90">
+        <v>0.637</v>
+      </c>
+      <c r="H90">
+        <v>28.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.64</v>
+      </c>
+      <c r="K90">
+        <v>0.921</v>
+      </c>
+      <c r="L90">
+        <v>1.719</v>
+      </c>
+      <c r="M90">
+        <v>6.73931808</v>
+      </c>
+      <c r="N90">
+        <v>-5.02031808</v>
+      </c>
+      <c r="O90">
+        <v>-1.25507952</v>
+      </c>
+      <c r="P90">
+        <v>-3.76523856</v>
+      </c>
+      <c r="Q90">
+        <v>-2.84423856</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.015069775246243</v>
+      </c>
+      <c r="T90">
+        <v>6.336121524997726</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.06376757928600396</v>
+      </c>
+      <c r="W90">
+        <v>0.2235723020665023</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2550703171440158</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3205519988480712</v>
+      </c>
+      <c r="C91">
+        <v>-13.76833094492476</v>
+      </c>
+      <c r="D91">
+        <v>14.13696905507524</v>
+      </c>
+      <c r="E91">
+        <v>25.1723</v>
+      </c>
+      <c r="F91">
+        <v>28.5423</v>
+      </c>
+      <c r="G91">
+        <v>0.637</v>
+      </c>
+      <c r="H91">
+        <v>28.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.64</v>
+      </c>
+      <c r="K91">
+        <v>0.921</v>
+      </c>
+      <c r="L91">
+        <v>1.719</v>
+      </c>
+      <c r="M91">
+        <v>6.815901240000001</v>
+      </c>
+      <c r="N91">
+        <v>-5.09690124</v>
+      </c>
+      <c r="O91">
+        <v>-1.27422531</v>
+      </c>
+      <c r="P91">
+        <v>-3.82267593</v>
+      </c>
+      <c r="Q91">
+        <v>-2.90167593</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.103821572995902</v>
+      </c>
+      <c r="T91">
+        <v>6.912132572724792</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.06305108963110503</v>
+      </c>
+      <c r="W91">
+        <v>0.2237433997960921</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2522043585244202</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3225519988480712</v>
+      </c>
+      <c r="C92">
+        <v>-14.18867407774826</v>
+      </c>
+      <c r="D92">
+        <v>14.03732592225174</v>
+      </c>
+      <c r="E92">
+        <v>25.493</v>
+      </c>
+      <c r="F92">
+        <v>28.863</v>
+      </c>
+      <c r="G92">
+        <v>0.637</v>
+      </c>
+      <c r="H92">
+        <v>28.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.64</v>
+      </c>
+      <c r="K92">
+        <v>0.921</v>
+      </c>
+      <c r="L92">
+        <v>1.719</v>
+      </c>
+      <c r="M92">
+        <v>6.8924844</v>
+      </c>
+      <c r="N92">
+        <v>-5.1734844</v>
+      </c>
+      <c r="O92">
+        <v>-1.2933711</v>
+      </c>
+      <c r="P92">
+        <v>-3.8801133</v>
+      </c>
+      <c r="Q92">
+        <v>-2.959113299999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.210323730295492</v>
+      </c>
+      <c r="T92">
+        <v>7.603345829997272</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.06235052196853721</v>
+      </c>
+      <c r="W92">
+        <v>0.2239106953539133</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2494020878741489</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3245519988480712</v>
+      </c>
+      <c r="C93">
+        <v>-14.60762239082281</v>
+      </c>
+      <c r="D93">
+        <v>13.93907760917719</v>
+      </c>
+      <c r="E93">
+        <v>25.8137</v>
+      </c>
+      <c r="F93">
+        <v>29.1837</v>
+      </c>
+      <c r="G93">
+        <v>0.637</v>
+      </c>
+      <c r="H93">
+        <v>28.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.64</v>
+      </c>
+      <c r="K93">
+        <v>0.921</v>
+      </c>
+      <c r="L93">
+        <v>1.719</v>
+      </c>
+      <c r="M93">
+        <v>6.969067560000001</v>
+      </c>
+      <c r="N93">
+        <v>-5.250067560000001</v>
+      </c>
+      <c r="O93">
+        <v>-1.31251689</v>
+      </c>
+      <c r="P93">
+        <v>-3.93755067</v>
+      </c>
+      <c r="Q93">
+        <v>-3.01655067</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.340493033661658</v>
+      </c>
+      <c r="T93">
+        <v>8.448162033330304</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.06166535139745438</v>
+      </c>
+      <c r="W93">
+        <v>0.2240743140862879</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2466614055898175</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3265519988480712</v>
+      </c>
+      <c r="C94">
+        <v>-15.02520496793767</v>
+      </c>
+      <c r="D94">
+        <v>13.84219503206233</v>
+      </c>
+      <c r="E94">
+        <v>26.1344</v>
+      </c>
+      <c r="F94">
+        <v>29.5044</v>
+      </c>
+      <c r="G94">
+        <v>0.637</v>
+      </c>
+      <c r="H94">
+        <v>28.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.64</v>
+      </c>
+      <c r="K94">
+        <v>0.921</v>
+      </c>
+      <c r="L94">
+        <v>1.719</v>
+      </c>
+      <c r="M94">
+        <v>7.04565072</v>
+      </c>
+      <c r="N94">
+        <v>-5.32665072</v>
+      </c>
+      <c r="O94">
+        <v>-1.33166268</v>
+      </c>
+      <c r="P94">
+        <v>-3.99498804</v>
+      </c>
+      <c r="Q94">
+        <v>-3.07398804</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.503204662869366</v>
+      </c>
+      <c r="T94">
+        <v>9.504182287496594</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.0609950758387864</v>
+      </c>
+      <c r="W94">
+        <v>0.2242343758896978</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2439803033551456</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3285519988480712</v>
+      </c>
+      <c r="C95">
+        <v>-15.44145008988398</v>
+      </c>
+      <c r="D95">
+        <v>13.74664991011602</v>
+      </c>
+      <c r="E95">
+        <v>26.4551</v>
+      </c>
+      <c r="F95">
+        <v>29.8251</v>
+      </c>
+      <c r="G95">
+        <v>0.637</v>
+      </c>
+      <c r="H95">
+        <v>28.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.64</v>
+      </c>
+      <c r="K95">
+        <v>0.921</v>
+      </c>
+      <c r="L95">
+        <v>1.719</v>
+      </c>
+      <c r="M95">
+        <v>7.122233880000001</v>
+      </c>
+      <c r="N95">
+        <v>-5.403233880000001</v>
+      </c>
+      <c r="O95">
+        <v>-1.35080847</v>
+      </c>
+      <c r="P95">
+        <v>-4.052425410000001</v>
+      </c>
+      <c r="Q95">
+        <v>-3.13142541</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.712405328993561</v>
+      </c>
+      <c r="T95">
+        <v>10.86192261428182</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.06033921480826181</v>
+      </c>
+      <c r="W95">
+        <v>0.2243909955037871</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2413568592330473</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3305519988480712</v>
+      </c>
+      <c r="C96">
+        <v>-15.85638526197803</v>
+      </c>
+      <c r="D96">
+        <v>13.65241473802197</v>
+      </c>
+      <c r="E96">
+        <v>26.7758</v>
+      </c>
+      <c r="F96">
+        <v>30.1458</v>
+      </c>
+      <c r="G96">
+        <v>0.637</v>
+      </c>
+      <c r="H96">
+        <v>28.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.64</v>
+      </c>
+      <c r="K96">
+        <v>0.921</v>
+      </c>
+      <c r="L96">
+        <v>1.719</v>
+      </c>
+      <c r="M96">
+        <v>7.198817040000001</v>
+      </c>
+      <c r="N96">
+        <v>-5.47981704</v>
+      </c>
+      <c r="O96">
+        <v>-1.36995426</v>
+      </c>
+      <c r="P96">
+        <v>-4.10986278</v>
+      </c>
+      <c r="Q96">
+        <v>-3.18886278</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.991339550492488</v>
+      </c>
+      <c r="T96">
+        <v>12.67224304999546</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.05969730826774839</v>
+      </c>
+      <c r="W96">
+        <v>0.2245442827856617</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2387892330709935</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3325519988480712</v>
+      </c>
+      <c r="C97">
+        <v>-16.27003724046028</v>
+      </c>
+      <c r="D97">
+        <v>13.55946275953972</v>
+      </c>
+      <c r="E97">
+        <v>27.0965</v>
+      </c>
+      <c r="F97">
+        <v>30.4665</v>
+      </c>
+      <c r="G97">
+        <v>0.637</v>
+      </c>
+      <c r="H97">
+        <v>28.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.64</v>
+      </c>
+      <c r="K97">
+        <v>0.921</v>
+      </c>
+      <c r="L97">
+        <v>1.719</v>
+      </c>
+      <c r="M97">
+        <v>7.275400200000001</v>
+      </c>
+      <c r="N97">
+        <v>-5.556400200000001</v>
+      </c>
+      <c r="O97">
+        <v>-1.38910005</v>
+      </c>
+      <c r="P97">
+        <v>-4.167300150000001</v>
+      </c>
+      <c r="Q97">
+        <v>-3.246300150000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.381847460590988</v>
+      </c>
+      <c r="T97">
+        <v>15.20669165999456</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.05906891554914051</v>
+      </c>
+      <c r="W97">
+        <v>0.2246943429668652</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.236275662196562</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3345519988480712</v>
+      </c>
+      <c r="C98">
+        <v>-16.68243205782315</v>
+      </c>
+      <c r="D98">
+        <v>13.46776794217685</v>
+      </c>
+      <c r="E98">
+        <v>27.4172</v>
+      </c>
+      <c r="F98">
+        <v>30.7872</v>
+      </c>
+      <c r="G98">
+        <v>0.637</v>
+      </c>
+      <c r="H98">
+        <v>28.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.64</v>
+      </c>
+      <c r="K98">
+        <v>0.921</v>
+      </c>
+      <c r="L98">
+        <v>1.719</v>
+      </c>
+      <c r="M98">
+        <v>7.35198336</v>
+      </c>
+      <c r="N98">
+        <v>-5.63298336</v>
+      </c>
+      <c r="O98">
+        <v>-1.40824584</v>
+      </c>
+      <c r="P98">
+        <v>-4.22473752</v>
+      </c>
+      <c r="Q98">
+        <v>-3.303737519999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.967609325738728</v>
+      </c>
+      <c r="T98">
+        <v>19.00836457499316</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.05845361434550363</v>
+      </c>
+      <c r="W98">
+        <v>0.2248412768942937</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2338144573820146</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3365519988480712</v>
+      </c>
+      <c r="C99">
+        <v>-17.09359504711814</v>
+      </c>
+      <c r="D99">
+        <v>13.37730495288186</v>
+      </c>
+      <c r="E99">
+        <v>27.7379</v>
+      </c>
+      <c r="F99">
+        <v>31.1079</v>
+      </c>
+      <c r="G99">
+        <v>0.637</v>
+      </c>
+      <c r="H99">
+        <v>28.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.64</v>
+      </c>
+      <c r="K99">
+        <v>0.921</v>
+      </c>
+      <c r="L99">
+        <v>1.719</v>
+      </c>
+      <c r="M99">
+        <v>7.42856652</v>
+      </c>
+      <c r="N99">
+        <v>-5.70956652</v>
+      </c>
+      <c r="O99">
+        <v>-1.42739163</v>
+      </c>
+      <c r="P99">
+        <v>-4.28217489</v>
+      </c>
+      <c r="Q99">
+        <v>-3.36117489</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>3.943879100984971</v>
+      </c>
+      <c r="T99">
+        <v>25.34448609999088</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.05785099976462215</v>
+      </c>
+      <c r="W99">
+        <v>0.2249851812562082</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2314039990584886</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3385519988480712</v>
+      </c>
+      <c r="C100">
+        <v>-17.50355086528976</v>
+      </c>
+      <c r="D100">
+        <v>13.28804913471024</v>
+      </c>
+      <c r="E100">
+        <v>28.0586</v>
+      </c>
+      <c r="F100">
+        <v>31.4286</v>
+      </c>
+      <c r="G100">
+        <v>0.637</v>
+      </c>
+      <c r="H100">
+        <v>28.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.64</v>
+      </c>
+      <c r="K100">
+        <v>0.921</v>
+      </c>
+      <c r="L100">
+        <v>1.719</v>
+      </c>
+      <c r="M100">
+        <v>7.505149680000001</v>
+      </c>
+      <c r="N100">
+        <v>-5.78614968</v>
+      </c>
+      <c r="O100">
+        <v>-1.44653742</v>
+      </c>
+      <c r="P100">
+        <v>-4.33961226</v>
+      </c>
+      <c r="Q100">
+        <v>-3.41861226</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>5.896418651477456</v>
+      </c>
+      <c r="T100">
+        <v>38.01672914998632</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.05726068344049335</v>
+      </c>
+      <c r="W100">
+        <v>0.2251261487944102</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2290427337619735</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3405519988480712</v>
+      </c>
+      <c r="C101">
+        <v>-17.91232351558164</v>
+      </c>
+      <c r="D101">
+        <v>13.19997648441836</v>
+      </c>
+      <c r="E101">
+        <v>28.3793</v>
+      </c>
+      <c r="F101">
+        <v>31.7493</v>
+      </c>
+      <c r="G101">
+        <v>0.637</v>
+      </c>
+      <c r="H101">
+        <v>28.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.64</v>
+      </c>
+      <c r="K101">
+        <v>0.921</v>
+      </c>
+      <c r="L101">
+        <v>1.719</v>
+      </c>
+      <c r="M101">
+        <v>7.581732840000001</v>
+      </c>
+      <c r="N101">
+        <v>-5.862732840000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.46568321</v>
+      </c>
+      <c r="P101">
+        <v>-4.397049630000001</v>
+      </c>
+      <c r="Q101">
+        <v>-3.47604963</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>11.75403730295491</v>
+      </c>
+      <c r="T101">
+        <v>76.03345829997264</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.05668229269867019</v>
+      </c>
+      <c r="W101">
+        <v>0.2252642685035576</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2267291707946808</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
